--- a/new_excel.xlsx
+++ b/new_excel.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:H41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -516,28 +516,28 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2003-08-17</t>
+          <t>2001-11-19</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.tribuneindia.com/news/business/delhi-home-minister-flags-off-aecl-season-7-amid-star-studded-launch-in-capital/</t>
+          <t>https://www.tribuneindia.com/news/entertainment/from-indie-to-masala-mrunal-thakur-embraces-commercial-comedy-in-son-of-sardaar-2/</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Delhi Home Minister Flags Off AECL Season 7 Amid Star-Studded Launch in Capital</t>
+          <t>From indie to masala: Mrunal Thakur embraces commercial comedy in 'Son of Sardaar 2'</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>New Delhi [India], July 16: After a year-long hiatus, the much-awaited Artist Event Cricket League (AECL) officially announced the launch of its 7th season, set to begin on September 13, 2025. The announcement was made at a glittering press conference held at The Zora, New Delhi, in the presence of esteemed dignitaries and celebrities from diverse fields. Gracing the occasion were Ajay Chaudhary (Special CP, Delhi Police), Atul Jain (Director, DS Group), Ashish Sood (Home Minister, Delhi), Rohan Jaitley (President, DDCA), Harsh Malhotra (Transport Minister), Amit Gupta (Orana Group), Sanjeev Chhibber, director of Galway, Amit Jidani, Director of Devam, Rituraj Khanna Q Events, Bobby Yash, director of Bobby Yash, Kaptaan laadi Piyush Chawla (Indian International Cricketer), Anil Chaudhary (International Umpire), singer Milind Gaba and music sensation Aditya Narayan. The founders of AECL - Ashish Mathur, Sonia Mathur, Ashish Rathee, and Vipul Gosai - unveiled the Season 7 schedule and introduced the participating teams and celebrity players. This season will witness an exciting inaugural friendly match between a celebrity team and Team Samarthanam, a visually challenged cricket team that represented India and became World Champions in 2018. This match is a heartfelt tribute by the entertainment and event industry to the inspiring athletes of Team Samarthanam. Speaking at the launch, Ashish Mathur, Founder of AECL, said: "With Season 7, we are raising the bar like never before. This season, we also launch a special book that celebrates AECL's incredible journey--our struggles, triumphs, and the vibrant community that has turned this league into a national platform. AECL has always been about unity, opportunity, and celebrating the spirit of the artist." This year's winners will take home a cash prize of ₹15 lakh, while the runner-up team will be awarded ₹2.5 lakh. The "Man of the Tournament" award has been divided into two categories - the Best Batsman will receive a m</t>
+          <t>Actor Mrunal Thakur on Friday said she had never imagined herself doing a full-blown commercial entertainer until ‘Son of Sardaar 2’ came her way. The actor, known for her roles in critically acclaimed films such as ‘Love Sonia’, ‘Super 30’, ‘Sita Ramam’ and ‘Hi Nanna’, expressed gratitude to co-star Ajay Devgn for encouraging her to explore the comedy genre. The upcoming action-comedy, a sequel to the 2012 hit ‘Son of Sardaar’, stars Devgn in the lead once again and is directed by Vijay Kumar Arora. “I loved troubling Jassi (Devgn’s character) in this film. There are four women troubling him in the story,” Thakur said at the trailer launch in Mumbai. “This is my first commercial film, and I’m grateful to Ajay sir and the director for giving me this opportunity. “I couldn’t imagine myself as Rabia, nor picture myself torturing Jassi on screen. I kept wondering, ‘Will I be able to pull this off?’ But with the help of Deepak sir (Dobriyal), Kubbra (Sait), Roshni, and later Chunky sir who joined in – we had a blast on set. Especially with Deepak sir, I had a lot of fun,” she added. The film features an ensemble cast including Ravi Kishan, Sanjay Mishra, Neeru Bajwa, Chunky Panday, Kubbra Sait, Deepak Dobriyal, Vindu Dara Singh, Roshni Walia, Sharat Saxena, Sahil Mehta and the late Mukul Dev. Kishan and Sait fondly remembered working with Dev, who passed away in May this year at the age of 54. “Mukul has been an old friend. We spent nearly 40 days together on this film,” Kishan said. “He was so excited about the project. You’ll love him in it – his jokes, his performance. We all love and miss Mukul. I’d suggest watching the film for him – he was a brilliant actor.” Sait echoed the sentiment, noting that Dev was always the first to arrive on set and remains deeply missed by the cast and crew. Originally, Sanjay Dutt was meant to reprise his role from the first film. However, a visa issue prevented him from joining the UK schedule, and Kishan was brought in to replace him</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Politics</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -554,28 +554,28 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2004-11-10</t>
+          <t>2002-01-03</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.tribuneindia.com/news/world/fbi-adds-3-iranian-intelligence-officers-to-wanted-list-over-levinson-case/</t>
+          <t>https://www.tribuneindia.com/news/a-broad-minded-liberal-308855/</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>FBI adds 3 Iranian intelligence officers to wanted list over Levinson case</t>
+          <t>Remembering our founder — Sardar Dyal Singh Majithia</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Washington [US], July 16 (ANI): The Federal Bureau of Investigation (FBI) has named three senior Iranian intelligence officers in connection with the 2007 abduction of retired FBI agent Robert A "Bob" Levinson from Kish Island in Iran, the US fedral agency said in a statement. The three men identified are Reza Amiri Moghadam, Taghi Daneshvar and Gholamhossein Mohammadnia. The FBI's Washington Field Office said the trio played key roles in Levinson's kidnapping and in efforts to hide Iran's involvement. "These three intelligence officers were among those who allegedly facilitated Bob's 2007 abduction and the subsequent cover-up by the Iranian government. Bob likely later perished in captivity far away from his family, friends, and colleagues," said Steven Jensen, Assistant Director in Charge of the Washington Field Office. "The FBI will continue its relentless pursuit to hold anyone involved in his abduction to account for their reprehensible actions." Reza Amiri Moghadam, an official of Iran’s Ministry of Intelligence and Security, is wanted for questioning based on his alleged involvement in the abduction, detention, and probable death of retired FBI Special Agent Robert A. Levinson: https://t.co/3jdNl5splA pic.twitter.com/WHvvTGo7kM — FBI Most Wanted (@FBIMostWanted) July 15, 2025 The FBI believes that Iranian intelligence services not only carried out the abduction but also spread false information to escape responsibility. Reza Amiri Moghadam, now serving as Iran's ambassador to Pakistan, previously led operations for the Ministry of Intelligence and Security (MOIS). The FBI says he was in charge of agents in Europe at the time Levinson disappeared, the FBI statement added. Taghi Daneshvar, who is known by several aliases, is another senior MOIS officer. He reportedly oversaw Mohammad Baseri, an MOIS officer who was sanctioned by the US earlier, during the time Levinson went missing. The third officer, Gholamhossein Mohammadnia, was Iran's ambassador to Albania.</t>
+          <t xml:space="preserve">SARDAR Dyal Singh Majithia came from a family that had played a very important part in the history of the Sikh state founded by Maharaja Ranjit Singh. For three generations, the family had provided generals to the Maharaja’s forces, and Dyal Singh’s father was in charge of the kingdom’s ordnance. His uncle, Gujar Singh, who had been deputed by Maharaja Ranjit to go to Calcutta on a diplomatic mission, was accompanied by 200 armed men specially chosen by the Maharaja. And when Dyal Singh’s father, Lehna Singh, left Lahore for a pilgrimage, his adversaries at the darbar in Lahore said that he too had gone with an escort of 200 and taken along gold worth a crore of rupees. Lehna Singh went to different pilgrimage centres and finally bought an estate in Kashi (Benaras). One yardstick to gauge the importance of a family in society in the British times was its placement in the list of protocol. And so eminent was Dyal Singh’s family that when the Viceregal darbar was held in Lahore in 1864, of the 603 people invited, Dyal Singh, then aged 16, was allotted the 55th seat, his uncle Ranjodh Singh the 103rd. While some members of the erstwhile ruling class lived a life of ease and indulgence, hankered after titles and jagirs, some others took up such jobs as that of tehsildar or extra-assistant commissioner, Dyal Singh decided to carve out a career for himself. Tall, well-built and handsome, with refined tastes and aristocratic bearing, he became a shrewd businessman dealing in real estate, precious stones and jewellery. The areas outside the walled city of Lahore had barracks for the British soldiers. After the British decided that a cantonment should be built in Mian Mir, the barracks were to be pulled down and the plots auctioned. Dyal Singh’s agents bid for the plots, and on these he constructed buildings to be rented out to high-ranking British civilians. When he died in 1898, he owned 26 valuable properties, including Dyal Singh Mansion with 54 residential units on The </t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Politics</t>
+          <t>Business</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -592,28 +592,28 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2005-01-13</t>
+          <t>2002-03-25</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://www.tribuneindia.com/news/world/fearing-collapse-taiwan-pulls-billions-from-chinas-crumbling-economy/</t>
+          <t>https://www.tribuneindia.com/news/sports/six-teams-to-battle-for-medals-in-los-angeles-olympics-in-2028/</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Fearing collapse, Taiwan pulls billions from China's crumbling economy</t>
+          <t>Six teams to battle for medals in Los Angeles Olympics in 2028</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Taipei [Taiwan], July 16 (ANI): Taiwan's financial exposure to China dropped sharply by the end of May, as concerns grow over China's slowing economy and political instability, Focus Taiwan reported. The Financial Supervisory Commission (FSC), Taiwan's top financial regulator, said on Monday that the total exposure of the island's banking, insurance and securities sectors to China fell by NT$201.3 billion, or nearly 20 per cent year-on-year, to NT$828.39 billion (US$28.25 billion). Focus Taiwan noted that this figure also marked a NT$48.56 billion drop compared to April. Although the FSC did not confirm if currency changes played a role, officials said the decline was mainly due to reduced risk-taking as China's economy and property market remain uncertain. Among the three sectors, banks made up the largest portion of exposure--NT$768.45 billion, or 92 per cent of the total. This was 18.67 per cent lower than a year ago. As a result, the banking sector's exposure-to-net-worth ratio with China fell to a record low of 15.9 per cent, Focus Taiwan reported. Chang Chia-kuei, chief secretary of the FSC's Banking Bureau, said Taiwanese banks had especially reduced interbank loans to China, which dropped by 35 per cent year-on-year. "The decline highlights increasing caution among Taiwanese lenders regarding China's economic trajectory and property sector risks," Focus Taiwan quoted him as saying. CTBC Bank had the highest exposure to China at NT$180 billion, followed by Taipei Fubon Bank at NT$85.8 billion, and Bank SinoPac at NT$62.5 billion. Their exposure-to-net-worth ratios were 49 per cent, 31.1 per cent, and 35.5 per cent respectively, according to Focus Taiwan. The insurance sector also saw a 30 per cent drop in investments in Chinese marketable securities, which totalled NT$49.9 billion. All of this came from life insurance companies. Tsai Huo-yen from the FSC's Insurance Bureau said these investments made up only 0.15 per cent of the industry's disposable capital.</t>
+          <t>Los Angeles [US], July 16 (ANI): Six teams each in the men's and women's categories are set to battle for medals in an upcoming tournament. With 90 athlete quotas allocated for each tournament, participating nations can name squads of up to 15 members. Following the announcement of the confirmed number of teams and the venue for LA28 back in April, the International Olympic Committee (IOC) has announced that the T20 competitions for the men's and women's categories at LA28 will run from July 12 to July 29, 2028. The medal matches will be held on 20 July (women's) and 29 July (men's) respectively. The announcement marks another landmark moment for the sport, which will be making its second-ever Olympic appearance - 128 years after its debut in Paris 1900, when Great Britain claimed gold in a one-off match against France. All matches will be staged at the Pomona Fairplex, about 50 km from downtown Los Angeles. The format includes double-headers on most matchdays, with fixtures beginning at 9:00 AM and 6:30 PM local time. The return of cricket to the Olympics signals another major step forward in the sport's global expansion, and to celebrate the game on one of the world's biggest sporting stages. The mode of qualification for the LA28 Olympic Games is yet to be confirmed, but will likely be discussed during the ICC's Annual Conference in Singapore starting on July 17. This is only the second time the sport has made an appearance at the Olympics since 1900. Back then, only two teams, Great Britain and France, had played a two-day match, with the former winning the gold medal. Cricket's inclusion in the Olympics demonstrates its growing popularity, with women's cricket making its Commonwealth Games debut in 2022 at Birmingham. Meanwhile, both men's and women's cricket have been part of the Asian Games programme since 2010, 2014, and 2023. Recently, during the ICC T20 World Cup last year, the USA co-hosted the event along with the West Indies, with Grand Prairie, Lauderh</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Business</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -630,28 +630,28 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2008-10-30</t>
+          <t>2003-08-17</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://www.tribuneindia.com/news/state/uttar-pradesh</t>
+          <t>https://www.tribuneindia.com/news/business/delhi-home-minister-flags-off-aecl-season-7-amid-star-studded-launch-in-capital/</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Uttar Pradesh</t>
+          <t>Delhi Home Minister Flags Off AECL Season 7 Amid Star-Studded Launch in Capital</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Uttar PradeshUP sisters share vulgar content with offensive language on Instagram for Rs 25,000 a month; 4 arrestedPolice began investigating after receiving complaints about such videos being posted from the Asmoli police station areaPTI</t>
+          <t>New Delhi [India], July 16: After a year-long hiatus, the much-awaited Artist Event Cricket League (AECL) officially announced the launch of its 7th season, set to begin on September 13, 2025. The announcement was made at a glittering press conference held at The Zora, New Delhi, in the presence of esteemed dignitaries and celebrities from diverse fields. Gracing the occasion were Ajay Chaudhary (Special CP, Delhi Police), Atul Jain (Director, DS Group), Ashish Sood (Home Minister, Delhi), Rohan Jaitley (President, DDCA), Harsh Malhotra (Transport Minister), Amit Gupta (Orana Group), Sanjeev Chhibber, director of Galway, Amit Jidani, Director of Devam, Rituraj Khanna Q Events, Bobby Yash, director of Bobby Yash, Kaptaan laadi Piyush Chawla (Indian International Cricketer), Anil Chaudhary (International Umpire), singer Milind Gaba and music sensation Aditya Narayan. The founders of AECL - Ashish Mathur, Sonia Mathur, Ashish Rathee, and Vipul Gosai - unveiled the Season 7 schedule and introduced the participating teams and celebrity players. This season will witness an exciting inaugural friendly match between a celebrity team and Team Samarthanam, a visually challenged cricket team that represented India and became World Champions in 2018. This match is a heartfelt tribute by the entertainment and event industry to the inspiring athletes of Team Samarthanam. Speaking at the launch, Ashish Mathur, Founder of AECL, said: "With Season 7, we are raising the bar like never before. This season, we also launch a special book that celebrates AECL's incredible journey--our struggles, triumphs, and the vibrant community that has turned this league into a national platform. AECL has always been about unity, opportunity, and celebrating the spirit of the artist." This year's winners will take home a cash prize of ₹15 lakh, while the runner-up team will be awarded ₹2.5 lakh. The "Man of the Tournament" award has been divided into two categories - the Best Batsman will receive a m</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Politics</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -668,28 +668,28 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2009-10-25</t>
+          <t>2004-03-17</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://www.tribuneindia.com/news/chhattisgarh/top-naxal-commander-among-27-shot-in-chhattisgarhs-bastar/</t>
+          <t>https://www.tribuneindia.com/news/business/stock-markets-edge-up-amid-weak-global-market-trends-tariff-related-uncertainty/</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Top Naxal commander among 27 shot in Chhattisgarh’s Bastar</t>
+          <t>Stock markets edge up amid weak global market trends, tariff-related uncertainty</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>The security forces on Wednesday achieved a major success in their operation against Maoists as 27 Naxals, including topmost leader Nambala Keshav Rao, aka Basavaraju, were killed in an encounter in the Abujhmad region of Chhattisgarh on the border of Narayanpur and Bijapur districts. A jawan of the Chhattisgarh Police’s District Reserve Guard (DRG) was also killed while a few other personnel sustained injuries in the encounter that had begun several days ago, sources in the state police said. The killing of Keshav Rao, a CPI-Maoist general secretary, has come as a shot in the arm for the security forces as they had recently busted a long-time base of the Naxalites located in Koreguttalu Hills of Bijapur district in Chhattisgarh (bordering Telangana). Thirtyone Naxals were killed and a huge cache of arms, ammunitions and explosives recovered. Four factories where weapons were being manufactured were also unearthed under the three-week-long offensive named Operation Black Forest. Keshav Raocarried a bounty of Rs 1.5 crore and was wanted in connection with several deadly attacks on security forces across multiple states. A native of Jiyyannapet village in Andhra Pradesh's Srikakulam district, he was the son of a school teacher. He studied engineering at Warangal Regional Engineering College (REC) before being drawn into student activism in the 1980s. After being arrested during a student union protest in 1980, he went underground and joined the Naxals. Over the next four decades, Rao rose through the ranks and became known for his meticulous planning, ruthless ambushes, expertise in jungle warfare and making IEDs. Security officials believe he was the mastermind behind the 2010 Dantewada attack, one of the deadliest ever on Indian forces, in which 76 CRPF jawans were killed in Chhattisgarh. Despite the massive bounty, Rao managed to remain elusive for decades. The National Investigation Agency (NIA) had no recent photographs or confirmed details about his age. Prime M</t>
+          <t>Benchmark stock indices Sensex and Nifty closed marginally higher in a range-bound trade on Wednesday as investors stayed on the sidelines amid weak global market trends and tariff-related uncertainty. Rising for the second day in a row, the 30-share BSE Sensex edged up 63.57 points or 0.08 per cent to settle at 82,634.48. During the day, it hit a high of 82,784.75 and a low of 82,342.94. The 50-share NSE Nifty ended 16.25 points or 0.06 per cent higher at 25,212.05. Among Sensex firms, Mahindra &amp; Mahindra, Tech Mahindra, State Bank of India, Infosys, Adani Ports and ITC were the major gainers. However, Eternal, Sun Pharma, Tata Steel, Tata Motors, Bajaj Finance and Bharat Electronics were among the major laggards. Tech Mahindra rose by 1.94 per cent ahead of its financial results that were announced after market hours. The company posted a 30 per cent jump in consolidated profit after tax to Rs 1,128.8 crore in the June quarter of FY26 over the year-ago period. Infosys rebounded by 1.5 per cent, helping the key indices close in green. Take your experience further with Premium access.Thought-provoking Opinions, Expert Analysis, In-depth Insights and other Member Only Benefits The Tribune, now published from Chandigarh, started publication on February 2, 1881, in Lahore (now in Pakistan). It was started by Sardar Dyal Singh Majithia, a public-spirited philanthropist, and is run by a trust comprising five eminent persons as trustees.The Tribune, the largest selling English daily in North India, publishes news and views without any bias or prejudice of any kind. Restraint and moderation, rather than agitational language and partisanship, are the hallmarks of the newspaper. It is an independent newspaper in the real sense of the term.The Tribune has two sister publications, Punjabi Tribune (in Punjabi) and Dainik Tribune (in Hindi). Remembering Sardar Dyal Singh Majithia</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Business</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -706,22 +706,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2010-04-14</t>
+          <t>2004-11-10</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://www.tribuneindia.com/news/upsc/exam-schedule</t>
+          <t>https://www.tribuneindia.com/news/world/fbi-adds-3-iranian-intelligence-officers-to-wanted-list-over-levinson-case/</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Exam Schedule</t>
+          <t>FBI adds 3 Iranian intelligence officers to wanted list over Levinson case</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Exam ScheduleCombined Medical Services Examination, 2025CMS Examination is conducted by the UPSC for recruitment of Medical Officers (Group A posts) to various government departments/organisationsTribune News Service</t>
+          <t>Washington [US], July 16 (ANI): The Federal Bureau of Investigation (FBI) has named three senior Iranian intelligence officers in connection with the 2007 abduction of retired FBI agent Robert A "Bob" Levinson from Kish Island in Iran, the US fedral agency said in a statement. The three men identified are Reza Amiri Moghadam, Taghi Daneshvar and Gholamhossein Mohammadnia. The FBI's Washington Field Office said the trio played key roles in Levinson's kidnapping and in efforts to hide Iran's involvement. "These three intelligence officers were among those who allegedly facilitated Bob's 2007 abduction and the subsequent cover-up by the Iranian government. Bob likely later perished in captivity far away from his family, friends, and colleagues," said Steven Jensen, Assistant Director in Charge of the Washington Field Office. "The FBI will continue its relentless pursuit to hold anyone involved in his abduction to account for their reprehensible actions." Reza Amiri Moghadam, an official of Iran’s Ministry of Intelligence and Security, is wanted for questioning based on his alleged involvement in the abduction, detention, and probable death of retired FBI Special Agent Robert A. Levinson: https://t.co/3jdNl5splA pic.twitter.com/WHvvTGo7kM — FBI Most Wanted (@FBIMostWanted) July 15, 2025 The FBI believes that Iranian intelligence services not only carried out the abduction but also spread false information to escape responsibility. Reza Amiri Moghadam, now serving as Iran's ambassador to Pakistan, previously led operations for the Ministry of Intelligence and Security (MOIS). The FBI says he was in charge of agents in Europe at the time Levinson disappeared, the FBI statement added. Taghi Daneshvar, who is known by several aliases, is another senior MOIS officer. He reportedly oversaw Mohammad Baseri, an MOIS officer who was sanctioned by the US earlier, during the time Levinson went missing. The third officer, Gholamhossein Mohammadnia, was Iran's ambassador to Albania.</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
@@ -744,28 +744,28 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2012-06-26</t>
+          <t>2005-01-13</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://www.tribuneindia.com/news/nation/sc-asks-assam-human-rights-panel-to-probe-police-encounters/</t>
+          <t>https://www.tribuneindia.com/news/world/fearing-collapse-taiwan-pulls-billions-from-chinas-crumbling-economy/</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>SC asks Assam human rights panel to probe police encounters</t>
+          <t>Fearing collapse, Taiwan pulls billions from China's crumbling economy</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>The Supreme Court on Wednesday directed the Assam Human Rights Commission (AHRC) to conduct an independent probe into over 171 police encounters that took place in the state between May 2021 and August 2022, in which proper procedure was allegedly not followed. “We entrust this matter to the Assam Human Rights Commission for necessary enquiry, independently and expeditiously. It must be ensured that victims and family members are given a fair opportunity,” a Bench of Justice Surya Kant and Justice N Kotiswar Singh said. It directed the AHRC, headed by a retired HC chief justice, to issue a public notice inviting claims of the aggrieved, while ensuring confidentiality. The Bench said a blanket direction based on a mere compilation of cases was not justified even as it noted that a few specific instances might warrant further evaluation. The top court issued these directions while disposing of a petition filed by Arif Md Yeasin Jwadder alleging fake encounters by the Assam Police. He had sought an independent investigation into more than 171 police encounters in the state. The Bench concluded that most of the instances of alleged non-compliance with procedural guidelines, laid down by the top court in 2014, highlighted by the petitioner appeared to be factually incorrect. Barring a few of the cases, it was difficult to conclude that there were flagrant violations of guidelines, the top court said. It granted liberty to the AHRC to initiate further investigations into the allegations of fake encounters and asked the Assam Government to extend cooperation and remove any institutional barriers in the inquiry process. It asked the AHRC to safeguard the privacy of the complainants and approach the matter with sensitivity. It directed the Assam State Legal Services Authority to provide legal aid to the kin of victims of alleged fake encounters. The Assam Government has contended that the 2014 guidelines for investigating police encounters were duly followed in the state and</t>
+          <t>Taipei [Taiwan], July 16 (ANI): Taiwan's financial exposure to China dropped sharply by the end of May, as concerns grow over China's slowing economy and political instability, Focus Taiwan reported. The Financial Supervisory Commission (FSC), Taiwan's top financial regulator, said on Monday that the total exposure of the island's banking, insurance and securities sectors to China fell by NT$201.3 billion, or nearly 20 per cent year-on-year, to NT$828.39 billion (US$28.25 billion). Focus Taiwan noted that this figure also marked a NT$48.56 billion drop compared to April. Although the FSC did not confirm if currency changes played a role, officials said the decline was mainly due to reduced risk-taking as China's economy and property market remain uncertain. Among the three sectors, banks made up the largest portion of exposure--NT$768.45 billion, or 92 per cent of the total. This was 18.67 per cent lower than a year ago. As a result, the banking sector's exposure-to-net-worth ratio with China fell to a record low of 15.9 per cent, Focus Taiwan reported. Chang Chia-kuei, chief secretary of the FSC's Banking Bureau, said Taiwanese banks had especially reduced interbank loans to China, which dropped by 35 per cent year-on-year. "The decline highlights increasing caution among Taiwanese lenders regarding China's economic trajectory and property sector risks," Focus Taiwan quoted him as saying. CTBC Bank had the highest exposure to China at NT$180 billion, followed by Taipei Fubon Bank at NT$85.8 billion, and Bank SinoPac at NT$62.5 billion. Their exposure-to-net-worth ratios were 49 per cent, 31.1 per cent, and 35.5 per cent respectively, according to Focus Taiwan. The insurance sector also saw a 30 per cent drop in investments in Chinese marketable securities, which totalled NT$49.9 billion. All of this came from life insurance companies. Tsai Huo-yen from the FSC's Insurance Bureau said these investments made up only 0.15 per cent of the industry's disposable capital.</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Politics</t>
+          <t>Business</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -782,28 +782,28 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2012-10-08</t>
+          <t>2005-05-22</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://www.tribuneindia.com/news/shaharnama/bicycle-rides-on-brahmaputras-banks-in-dibrugarh/</t>
+          <t>https://www.tribuneindia.com/news/business/cabinet-approves-6-year-programme-to-improve-agriculture-productivity-in-100-districts/</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Bicycle rides on Brahmaputra’s banks in Dibrugarh</t>
+          <t>Cabinet approves 6-year programme to improve agriculture productivity in 100 districts</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Some memories never fade away — of places, of people and neighbourhoods, and remain as fresh and vivid as if they happened yesterday. My visits to Dibrugarh, Assam, on the banks of Brahmaputra, famous for its vast tea plantations, are part of such memories. My parents took me and my sibling to this quaint town during our summer holidays to our grandparents’ home. They lived in a place called Tinkunia, very close to the embankment of the Brahmaputra river. During the visits, we would routinely go for strolls along the embankment. The views of the Brahmaputra river flowing majestically and the stunning landscape dotted with trees and a row of colonial buildings-turned-offices and courts used to be breath-taking. There was a rickety wooden pier extending to the river and we used to tread carefully, lest our chappals got stuck in the gaps in between the wooden planks. I also learnt how to ride a bicycle, falling and tripping, ripping my knees so many times. I would frequent Graham Bazaar on bicycle with my uncle, where we would relish dosas, rounding it off with the special meetha paan from the famous Sukhlal paan dukan. I also loved to visit the lush tea gardens dotting the town and also the sprawling campus of Assam Medical College &amp; Hospital. I drive other vehicles now but the memories of my childhood days and maiden cycle rides in Dibrugarh often flash in my mind. Take your experience further with Premium access.Thought-provoking Opinions, Expert Analysis, In-depth Insights and other Member Only Benefits The Tribune, now published from Chandigarh, started publication on February 2, 1881, in Lahore (now in Pakistan). It was started by Sardar Dyal Singh Majithia, a public-spirited philanthropist, and is run by a trust comprising five eminent persons as trustees.The Tribune, the largest selling English daily in North India, publishes news and views without any bias or prejudice of any kind. Restraint and moderation, rather than agitational language and partisanship, ar</t>
+          <t xml:space="preserve">New Delhi [India], July 16 (ANI): Prime Minister Narendra Modi-chaired Union Cabinet, in a meeting on Wednesday, approved the Prime Minister Dhan-Dhaanya Krishi Yojana, which was initially announced in the Budget for 2025-26. The scheme aims to enhance agricultural productivity, increase crop diversification and sustainable agricultural practices, augment post-harvest storage, improve irrigation facilities and facilitate availability of credit. This programme will help 1.7 crore farmers, Union Minister Ashwini Vaishnaw told reporters today after the weekly Cabinet meeting. A financial outlay of Rs 24,000 crore will be earmarked per year, at least for 6 years starting 2025-26. Motivated by the success of the Aspirational Districts Programme, Finance Minister Nirmala Sitharaman had on February 1 proposed that the government will undertake a 'Prime Minister Dhan-Dhaanya Krishi Yojana' in partnership with states. It is in pursuance of Budget announcement for 2025-26 to develop 100 districts under "Prime Minister Dhan-Dhaanya Krishi Yojana". The Scheme will be implemented through convergence of 36 existing schemes across 11 Departments, other State schemes and local partnerships with the private sector. 100 districts will be identified based on three key indicators of low productivity, low cropping intensity, and less credit disbursement. The number of districts in each state/UT will be based on the share of Net Cropped Area and operational holdings. However, a minimum of 1 district will be selected from each state. Committees will be formed at District, State and National level for effective planning, implementation and monitoring of the Scheme. A District Agriculture and Allied Activities Plan will be finalized by the District Dhan Dhaanya Samiti, which will also have progressive farmers as members. The District Plans will be aligned to the national goals of crop diversification, conservation of water and soil health, self-sufficiency in agriculture and allied sectors </t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Politics</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -820,28 +820,28 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2013-05-13</t>
+          <t>2006-11-15</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://www.tribuneindia.com/news/nation/rural-health-officer-shot-in-patna/</t>
+          <t>https://www.tribuneindia.com/news/entertainment/rannvijay-to-host-chhoriyan-chali-gaon/</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Rural health officer shot in Patna</t>
+          <t>Rannvijay to host Chhoriyan Chali Gaon</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>A 50-year-old rural health officer was shot dead in Patna’s Pipra locality, officials said on Sunday. The deceased has been identified as Surendra Kumar. The incident occurred on Saturday night in Sheikhpura village while Kumar was working in a field. “According to villagers, they heard gunshots from the field, and when they rushed there, the officer was found lying unconscious with bullet injuries,” said Masaurhi Sub-Divisional Police Officer Kanhaiya Singh. Kumar, reportedly associated with the BJP, was taken to a nearby hospital where he succumbed to his injuries during treatment, Singh added. The body has been sent for post-mortem examination and an investigation is underway. The killing comes amid a spate of violent crimes in the Bihar capital over the past week. On July 10, a man linked to the sand mining trade was shot dead outside his home in Ranitalab. On July 4, prominent industrialist Gopal Khemka was murdered in Patna, sparking widespread public and political outrage. Take your experience further with Premium access.Thought-provoking Opinions, Expert Analysis, In-depth Insights and other Member Only Benefits The Tribune, now published from Chandigarh, started publication on February 2, 1881, in Lahore (now in Pakistan). It was started by Sardar Dyal Singh Majithia, a public-spirited philanthropist, and is run by a trust comprising five eminent persons as trustees.The Tribune, the largest selling English daily in North India, publishes news and views without any bias or prejudice of any kind. Restraint and moderation, rather than agitational language and partisanship, are the hallmarks of the newspaper. It is an independent newspaper in the real sense of the term.The Tribune has two sister publications, Punjabi Tribune (in Punjabi) and Dainik Tribune (in Hindi). Remembering Sardar Dyal Singh Majithia</t>
+          <t>Zee TV is set to launch Chhoriyan Chali Gaon, a reality series that bridges the gap between urban India and rural Bharat. The show follows 12 independent, urban women as they leave behind their fast-paced city lives to live for over 60 days in a traditional Indian village. Without access to gadgets or modern luxuries, they must embrace rural life — taking on daily chores, cooking on a ‘chulha’ and integrating with village customs. The format blends cultural immersion, emotional evolution and competitive social strategy. Actor Rannvijay Singha is set to host the series. “This isn’t just another reality show — it’s a mindset shift,” he said. “In an age of instant gratification, Chhoriyan Chali Gaon highlights the power of effort, connection and simplicity. It’s about rediscovering resilience.” Take your experience further with Premium access.Thought-provoking Opinions, Expert Analysis, In-depth Insights and other Member Only Benefits The Tribune, now published from Chandigarh, started publication on February 2, 1881, in Lahore (now in Pakistan). It was started by Sardar Dyal Singh Majithia, a public-spirited philanthropist, and is run by a trust comprising five eminent persons as trustees.The Tribune, the largest selling English daily in North India, publishes news and views without any bias or prejudice of any kind. Restraint and moderation, rather than agitational language and partisanship, are the hallmarks of the newspaper. It is an independent newspaper in the real sense of the term.The Tribune has two sister publications, Punjabi Tribune (in Punjabi) and Dainik Tribune (in Hindi). Remembering Sardar Dyal Singh Majithia</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Politics</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -858,28 +858,28 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2015-06-24</t>
+          <t>2007-07-03</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://www.tribuneindia.com/news/remembering-bn-goswamy/</t>
+          <t>https://www.tribuneindia.com/news/entertainment/silaa-unleashed-sadia-khateeb-breaks-the-mould-with-her-boldest-role/</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Remembering B N Goswamy</t>
+          <t>Silaa unleashed: Sadia Khateeb breaks the mould with her boldest role</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Remembering B N GoswamyThe world of craftswomenI haven’t read it myself, but someone narrated to me a story by U.R. Anantamurthy once in which the writer speaks feelingly about the two very different worlds inhabited by men and women of the same family in a traditional, well-to-do...B.N. Goswamy</t>
+          <t>After the success of The Diplomat, Sadia Khateeb steps into her most intense role yet in Omung Kumar’s upcoming action-drama Silaa, blending emotion, grit and high-octane sequences. Marking a significant shift from her earlier portrayals, Silaa introduces Khateeb in a fierce, raw avatar — one that promises to surprise audiences and redefine her on-screen persona. The makers recently unveiled the character poster, revealing a bold new look that hints at the emotional depth and tenacity of her role. Take your experience further with Premium access.Thought-provoking Opinions, Expert Analysis, In-depth Insights and other Member Only Benefits The Tribune, now published from Chandigarh, started publication on February 2, 1881, in Lahore (now in Pakistan). It was started by Sardar Dyal Singh Majithia, a public-spirited philanthropist, and is run by a trust comprising five eminent persons as trustees.The Tribune, the largest selling English daily in North India, publishes news and views without any bias or prejudice of any kind. Restraint and moderation, rather than agitational language and partisanship, are the hallmarks of the newspaper. It is an independent newspaper in the real sense of the term.The Tribune has two sister publications, Punjabi Tribune (in Punjabi) and Dainik Tribune (in Hindi). Remembering Sardar Dyal Singh Majithia</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>General News</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -896,28 +896,28 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2015-11-14</t>
+          <t>2007-09-13</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://www.tribuneindia.com/news/diaspora/sikh-mp-dhesi-says-afghan-nationals-at-risk-slams-uk-govt-over-data-leak/</t>
+          <t>https://www.tribuneindia.com/news/premium/love-stories-are-the-flavour-of-the-monsoon-season/</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>British MP Tanmanjeet Dhesi says 'Afghan nationals at risk', slams UK govt over data leak</t>
+          <t>Love stories are the flavour of the monsoon season</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>British MP Tanmanjeet Singh Dhesi, Chair of Parliament’s Defence Select Committee, has strongly criticised the UK government over its handling of a sensitive data breach that exposed thousands of Afghan nationals to potential danger. In an interview with Times Radio following the lifting of a long-standing court gag order, Dhesi described the situation as “an absolute mess and wholly unacceptable.” “It’s shameful that those Afghans who bravely supported our service personnel are now at risk,” he said. “I am minded to launch a committee investigation.” Dhesi, a senior Labour MP representing Slough, a diverse town west of London, was elected in 2017 as the UK’s first turbaned Sikh parliamentarian. Before entering national politics, he served as mayor of Gravesend, a historic riverside town in Kent with a sizeable South Asian population. The incident stems from a 2022 error by a Ministry of Defence (MoD) official, who mistakenly sent a spreadsheet containing the personal details of more than 33,000 Afghan citizens applying for resettlement in the UK under the Afghan Relocations and Assistance Policy (ARAP). Many of those listed had worked alongside British troops during the war. In an effort to contain the fallout, the government secured a superinjunction in September 2023 — a rarely used legal tool that barred any mention of the case, even its existence. That order was lifted earlier this week following a prolonged legal challenge by The Times and other British media outlets. Delivering his judgment last Tuesday, Justice Chamberlain warned that the sweeping secrecy created a “scrutiny vacuum” and “shut down the ordinary mechanisms of accountability which operate in a democracy.” In the House of Commons on Tuesday, UK Defence Secretary John Healey acknowledged the government’s mishandling of the issue: “I feel deeply uncomfortable about what happened. I apologize on behalf of the government to those affected.” An independent review, commissioned by a former senior civi</t>
+          <t>As the monsoon romances pour in this season, Hindi cinema is experiencing a refreshing resurgence of love stories that are as diverse as they are heartfelt. From urban complexities in Metro... In Dino to the raw emotional turbulence of Saiyaara, the big screen is echoing with tales of love, heartbreak and longing. Take your experience further with Premium access.Thought-provoking Opinions, Expert Analysis, In-depth Insights and other Member Only Benefits The Tribune, now published from Chandigarh, started publication on February 2, 1881, in Lahore (now in Pakistan). It was started by Sardar Dyal Singh Majithia, a public-spirited philanthropist, and is run by a trust comprising five eminent persons as trustees.The Tribune, the largest selling English daily in North India, publishes news and views without any bias or prejudice of any kind. Restraint and moderation, rather than agitational language and partisanship, are the hallmarks of the newspaper. It is an independent newspaper in the real sense of the term.The Tribune has two sister publications, Punjabi Tribune (in Punjabi) and Dainik Tribune (in Hindi). Remembering Sardar Dyal Singh Majithia</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Politics</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -934,22 +934,22 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2016-02-21</t>
+          <t>2007-12-14</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://www.tribuneindia.com/news/business/amdark-limited-launches-comprehensive-investment-fraud-recovery-program-to-combat-online-scam/</t>
+          <t>https://www.tribuneindia.com/news/business/businesses-must-embed-agentic-ai-workflows-for-scalability-and-strategic-advantage-deloitte/</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Amdark Limited Launches Comprehensive Investment Fraud Recovery Program to Combat online Scam</t>
+          <t>Businesses must embed agentic AI workflows for scalability and strategic advantage: Deloitte</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>New Delhi [India], July 16: Amdark Limited, a global leader in financial recovery and digital forensic services, today introduced its expanded Investment Fraud Recovery Program, designed to help victims of online scams--including cryptocurrency, forex, binary options, Ponzi schemes, and phishing attacks--reclaim lost funds and secure legal redress. Rising Threat of Online Investment Scams Digital investment fraud is escalating dramatically. From deceptive crypto scams to high-pressure forex and binary trading schemes, victims face significant financial losses and limited recovery options. As noted by GlobeNewswire, "online scams have become a significant concern in the digital finance space," targeting both novice and institutional investors. Due to the irreversible nature of cryptocurrency transactions, many victims find themselves stranded, often unable to trace stolen funds through conventional banking systems. Amdark Limited: Expertise in Forensics and Legal Advocacy Amdark Limited specializes in asset recovery through a unique combination of blockchain forensics, legal strategy, and global collaboration. Their comprehensive approach includes: * Advanced Forensic Technology: Cutting-edge tools trace digital asset flows across multiple environments, even when criminals use obfuscation tactics. * Global Legal Network: Amdark's team of forensic experts and international lawyers ensures victims receive jurisdictional legal support, from filing complaints to asset freezes. * Tailored Case Management: Through thorough case evaluation--from wallet address collection to communication correspondence--Amdark delivers personalized recovery strategies . "We empower victims by combining forensic precision with legal acumen, offering them the best chance to recover and seek justice," said Alan Kalbfell, spokesperson for Amdark Limited. Aligned with this year's surge in digital fraud, Amdark Limited has significantly broadened its service portfolio: Handling cases from phishin</t>
+          <t>New Delhi [India] July 16 (ANI): To fully harness the power of Agentic AI, businesses should embed multi-agent workflows into their core operations, noted a recent report by Deloitte. These workflows serve as intelligent backbones that manage end-to-end processes more efficiently. Deloitte further suggests that scalability should be built on reusability, developing modular agents designed for specific tasks that can be recombined for broader applications. This modularity not only saves development time but also accelerates deployment across use cases. According to the report, integration is another critical factor. Rather than replacing existing systems, Agentic AI should be layered onto current infrastructures, complementing existing automation tools, machine learning models, and enterprise software. The report further notes that this approach ensures smooth adoption and maximises existing technology investments. At the same time, companies must take a long-term view by architecting AI-ready systems that are scalable, interoperable, and aligned with future goals. This includes building data strategies, infrastructure, and governance models that can support evolving AI capabilities over the next five years. Additionally, one of the most strategic steps an organisation can take is to build native Agentic AI capabilities. Relying solely on third-party providers can limit innovation and competitive differentiation. By developing internal expertise and proprietary systems, businesses gain strategic control and the ability to respond faster to changing demands. Native capabilities also ensure that AI initiatives are aligned closely with business objectives and values. Finally, scaling Agentic AI requires a shift from isolated pilots to enterprise-grade frameworks. This means building unified governance around data security, model monitoring, risk management, and ethical AI practices. Collaboration across private and public sectors will be key in establishing responsible,</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
@@ -972,28 +972,28 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2016-11-16</t>
+          <t>2008-10-30</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://www.tribuneindia.com/news/world/madhya-pradesh-govt-committed-to-providing-best-facilities-to-youth-interested-in-football-mp-cm-mohan-yadav/</t>
+          <t>https://www.tribuneindia.com/news/state/uttar-pradesh</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>"Madhya Pradesh govt committed to providing best facilities to youth interested in football": MP CM Mohan Yadav</t>
+          <t>Uttar Pradesh</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Madrid [Spain], July 16 (ANI): Madhya Pradesh Chief Minister Dr Mohan Yadav on Wednesday visited the headquarters of Spain's top football league, La Liga, in Madrid and reiterated the state government's commitment to enhancing sports infrastructure, especially for the youth interested in football. During his visit, Yadav met senior La Liga officials and discussed potential avenues of cooperation in the areas of sports development and youth training. Speaking to ANI, the Madhya Pradesh Chief Minister said, "I visited the La Liga office where players from different countries play and young talents are nurtured by providing good training and facilities... La Liga is playing a huge role in promoting football." Highlighting that La Liga has signed an MoU with both the Union and the State Government, CM Yadav underscored, "The Madhya Pradesh government is committed to providing the best facilities to the youth interested in playing football so that they can bring laurels to the country in sports." The visit to La Liga was part of CM Yadav's ongoing official tour to Spain, which is focused on attracting global investment, encouraging technology exchange, and generating employment opportunities under the "Global Dialogue 2025" initiative. Yadav is currently on the second leg of his two-nation tour. He reached the Spanish capital after completing a three-day visit to the United Arab Emirates on Tuesday. According to a post on X by the Madhya Pradesh Chief Minister's Office (CMO), Yadav met senior La Liga officials and discussed possible cooperation in sports and youth development. The discussions covered a range of topics, including infrastructure support, grassroots development, and football training. "Chief Minister Dr. Mohan Yadav, during his visit to Madrid, Spain, visited the La Liga office and held discussions with senior officials to explore collaboration in sports and youth development. The discussions focused on football training, grassroots development, and infrast</t>
+          <t>Uttar PradeshUP sisters share vulgar content with offensive language on Instagram for Rs 25,000 a month; 4 arrestedPolice began investigating after receiving complaints about such videos being posted from the Asmoli police station areaPTI</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Politics</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1010,22 +1010,22 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2018-06-08</t>
+          <t>2009-06-22</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://www.tribuneindia.com/news/shaharnama/the-joys-of-visiting-the-city-of-joy/</t>
+          <t>https://www.tribuneindia.com/news/state/himachal/himachal-calling</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>The joys of visiting the City of Joy</t>
+          <t>Himachal Calling</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>I first visited Kolkata as a child when my father took us to the City of Joy during school holidays in the early 80s. I remember the long train journey from our hometown, Guwahati. We would often visit the famous Victoria Memorial, and go around the surrounding green sprawling Maidan on horse-drawn buggies. For going around the city, we would use its iconic yellow taxis to see its other famous landmarks like the Howrah Bridge, Vidyasagar Setu and other imposing colonial-era buildings on the banks of Hooghly. It was the only metropolis with tram services and we loved hopping onto the slow-moving electric trams that navigated its busy streets alongside other vehicles. We also enjoyed travelling the Metro there, which was the country's first metro service. Most of our evenings were spent frequenting the Esplanade and the Chowringhee for shopping, and savouring the street food there, as well as gorging on a wide variety of mishti (sweets) and faluda. Chinatown (Tiriti Bazaar) was another of our favourite destinations. Kolkata remains the only place where you can still find hand-pulled rickshaws plying in its alleys and by-lanes. As a kid I enjoyed riding in these rickshaws. I also have fond memories of New Year celebrations in the famous Park Street during later visits. Even now Kolkata never fails to fascinate me. Every time I visit, it still has more surprises offer. Take your experience further with Premium access.Thought-provoking Opinions, Expert Analysis, In-depth Insights and other Member Only Benefits The Tribune, now published from Chandigarh, started publication on February 2, 1881, in Lahore (now in Pakistan). It was started by Sardar Dyal Singh Majithia, a public-spirited philanthropist, and is run by a trust comprising five eminent persons as trustees.The Tribune, the largest selling English daily in North India, publishes news and views without any bias or prejudice of any kind. Restraint and moderation, rather than agitational language and partisanship, a</t>
+          <t>Himachal CallingOf 655 pharmaceutical units, mere 122 register for upgrade in Himachal#HIMACHALCALLING: With cases of drug samples failing quality parameters coming to the fore, the need to introduce quality was a key concernAmbika Sharma</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
@@ -1048,28 +1048,28 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2018-07-08</t>
+          <t>2009-07-26</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://www.tribuneindia.com/news/world/mp-cm-mohan-yadav-visits-la-liga-hq-in-madrid-discusses-sports-collaboration/</t>
+          <t>https://www.tribuneindia.com/news/sports/mohun-bagan-super-giant-fans-have-an-intimidating-factor-jamie-maclaren/</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>MP CM Mohan Yadav visits La Liga HQ in Madrid, discusses sports collaboration</t>
+          <t>Mohun Bagan Super Giant fans have an intimidating factor: Jamie Maclaren</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Madrid [Spain], July 16 (ANI): Madhya Pradesh Chief Minister Mohan Yadav on Wednesday visited the headquarters of Spain's top football league, La Liga, in Madrid. The visit was part of his official tour to Spain, aimed at attracting global investment to the state, encouraging technology exchange, and creating jobs under the "Global Dialogue 2025" initiative. Yadav is currently on the second leg of his two-nation tour. He reached the Spanish capital after completing a three-day visit to the United Arab Emirates on Tuesday. According to a post on X by the Madhya Pradesh Chief Minister's Office (CMO), Yadav met senior La Liga officials and discussed possible cooperation in sports and youth development. The discussions covered a range of topics, including infrastructure support, grassroots development, and football training. "Hon'ble Chief Minister Dr. Mohan Yadav, during his visit to Madrid, Spain, visited the LaLiga office and held discussions with senior officials to explore collaboration in sports and youth development. The discussions focused on football training, grassroots development, and infrastructure support in Madhya Pradesh. This visit reflects the state's vision to empower youth through global sports partnerships," The MP CMO stated on X. Yadav will remain in Spain until July 19. During his stay, he is scheduled to hold bilateral meetings with India's Ambassador to Spain, Dinesh K Patnaik, and explore business and investment opportunities in Madhya Pradesh. He will also take part in a leadership dialogue, interact with business forums in Madrid and Barcelona, meet members of the Indian community, and go on an industry tour. Earlier in the day, Yadav arrived in Madrid, leading a high-level delegation as part of his official visit to Spain. Yadav and his delegation were received at the Madrid Barajas Airport by India's Ambassador to Spain, Dinesh K Patnaik. Sharing the pictures of the MP CM's arrival, the Indian embassy in Spain wrote, "High-level delegation</t>
+          <t>New Delhi [India], July 16 (ANI): Mohun Bagan Super Giant forward Jamie Maclaren acknowledged that the Mariners' unwavering support throughout the campaign played a pivotal role in the team winning the Indian Super League (ISL) double for the first time in the club's history. Maclaren joined the Kolkata giants ahead of the 2024-25 season, and the expectations were high from the blockbuster signing. The Australian international, despite battling against an injury in the earlier games, scored 12 goals in his debut ISL season and was the top scorer for the Mariners, as per the press release from ISL. Great movement, precise headers, sharp footwork in the final third -- Maclaren was a complete package in the forward line. The MBSG striker racked up two assists, created 16 chances, won 31 duels, while maintaining a 34.29% goal conversion rate. But the most important aspect that he brought to the Mohun Bagan Super Giant setup was scoring when it mattered the most. "I'd like to think that I stood up when I was needed. I did it in the final, scoring the winner. I dreamt of those moments and eventually did that, and winning the double was super special with a great bunch of people, from the city, the staff, and the fans," he told MBSG TV in an interview. While quizzed about his favourite goal wearing the MBSG jersey, Maclaren picked two different strikes for different reasons. "From an emotional point of view, I would say the final because it was such a big game. It wasn't a screamer goal, but it was my type of goal, where I sniffed out a chance. I just knew Greg (Stewart) was going to put it in the box, and I had to be ready. Teams were tired, and I was still relatively fresh to get that decisive moment. You could see in my celebration that I was just waiting for that moment all year. To do it in front of our fans was special," he shared. "But from a quality point of view, I would say the goal in Kochi, where it took Vishal (Kaith), flicked on by Apuia. I touched it to Jaso</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Politics</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1086,22 +1086,22 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2018-12-26</t>
+          <t>2009-09-26</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://www.tribuneindia.com/news/world/indonesias-11-year-old-aura-farmer-dikha-wins-hearts-then-scholarship-government-title/</t>
+          <t>https://www.tribuneindia.com/news/sports/karnataka-hc-orders-state-government-to-make-public-disclosure-of-rcb-stampede-report/</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Indonesia’s 11-year-old ‘aura farmer’ Dikha wins hearts, then scholarship, government title</t>
+          <t>Karnataka HC orders state government to make public disclosure of RCB stampede report</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>The boat-dancing kid, Rayyan Arkan Dikha, has become internet’s favourite since a video of him dancing on the tip of a boat during the Pacu Jalur boat race in Riau province of Indonesia, went viral. diego luna really hit that 😂 pic.twitter.com/AC69ec8y3U — Major League Soccer (@MLS) July 2, 2025 Dikha’s traditional outfit, slick sunglasses, calm expression and hypnotic moves have made him an overnight global sensation who’s been dubbed the ultimate ‘aura farmer’ by the internet. Now, his hometown is giving him his flowers. According to reports by Hindustan Times, the government of Riau named Dika a tourism ambassador last week, celebrating his role in reviving culture among local kids. Governor Abdul Wahid also rewarded the 11-year-old a scholarship worth 20 million rupiah (around $1,200 USD). The official ceremony featured Dikha doing what he does best – dancing, this time alongside the governor himself. Also read: ‘Came up with it myself’: Indonesian boy’s dance on boat goes viral, inspires Travis Kelce “Wow, I am so happy,” Dika said in Indonesian in the government’s official announcement. “I never imagined I would meet the governor.” Dika has not just danced for fun, he served as a Tukang Tari, or dancer, whose job is to energise the rowers during the Pacu Jalur races. He’s been doing this since he was 9 years old, but this year, his performance resonated globally. Take your experience further with Premium access.Thought-provoking Opinions, Expert Analysis, In-depth Insights and other Member Only Benefits The Tribune, now published from Chandigarh, started publication on February 2, 1881, in Lahore (now in Pakistan). It was started by Sardar Dyal Singh Majithia, a public-spirited philanthropist, and is run by a trust comprising five eminent persons as trustees.The Tribune, the largest selling English daily in North India, publishes news and views without any bias or prejudice of any kind. Restraint and moderation, rather than agitational language and partisanshi</t>
+          <t>Bengaluru (Karnataka) [India], July 16 (ANI): The Karnataka High Court has ordered the state government to publicly disclose its status report on the stampede incident outside the M Chinnaswamy Stadium that occured during the celebrations of the Royal Challengers Bengaluru (RCB) team's maiden Indian Premier League (IPL) title win. The unfortunate tragedy led to the death of 11 people and left over 50 injured. The state government had requested the High Court to keep the report confidential, but as per ESPNCricinfo, the court on Monday categorically stated that there were no legal grounds for such confidentiality and they were merely "facts as perceived" by the government. The court has also directed the state government to furnish the reports to the other parties involved in the case, the RCB franchise, Karnataka State Cricket Association (KSCA), DNA Entertainment Networks, the event partner of the Red and Gold franchise. The franchise is however currently awaiting details which will come out after a thorough CID investigation. The team and DNA's top authorities have submitted their testimonies over the past one month. A date for delivery of judgement is yet to be made public. On July 1, the two-member bench of the Central Administrative Tribunal (CAT), a quasi-judicial body handling matters related to government and public servants, made some key observations about the crowd that gathered outside the team's home base. The CAT noted that the franchise was responsible for drawing a crowd of around three to five lakhs outside the venue to participate in the celebratory victory parade, which was announced by the team on all their social media handles shortly after defeating Punjab Kings (PBKS) to end the 18-year wait for the cup on June 3. The CAT was given a task to investigate the matter after Vikash Kumar, the Inspector General and Additional Commissioner of Police, Bengaluru (West), filed a complaint seeking redressal after his dismissal by Chief Minister Siddharam</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
@@ -1124,28 +1124,28 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2019-04-30</t>
+          <t>2009-10-25</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>https://www.tribuneindia.com/news/delhi/on-a-literary-pilgrimage-to-kolkatas-college-street/</t>
+          <t>https://www.tribuneindia.com/news/chhattisgarh/top-naxal-commander-among-27-shot-in-chhattisgarhs-bastar/</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>On a literary pilgrimage to Kolkata’s College Street</t>
+          <t>Top Naxal commander among 27 shot in Chhattisgarh’s Bastar</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">As someone who hails from Delhi, a city bustling with political discourse and historical gravitas, the idea of visiting Kolkata’s College Street had long fascinated me. Called Boi Para (book town) locally, it is more than just a marketplace; it is a cultural phenomenon. On a crisp winter morning, I boarded a flight to Kolkata with only one purpose: to spend a full day in the legendary book haven. College Street was unlike anything I had experienced in Delhi. While the Sunday book bazaar in Mahila Haat near Delhi Gate has its own charm, there was no beating the raw intellectual energy that coursed through College Street. As soon as I arrived in this largest book market in India and the largest second-hand book market in the world, I was struck by the sheer density of bookstalls—hundreds of them, stretching endlessly on both sides of the road, manned by sellers who knew the exact location of any book — be it a rare Bengali translation of Dostoevsky or a weathered copy of Malgudi Days or Mulk Raj Anand’s Coolie, without even looking. People of all ages didn’t just buy books — they argued about them, recommended them to strangers, and flipped through pages with a reverence. I began my exploration with Bengali classics — Rabindranath Tagore’s famous Ghare Baire (The Home and the World), Sarat Chandra Chattopadhyay’s Srikanta, and Bibhutibhushan Bandyopadhyay’s Pather Panchali. I also picked up a collection of Satyajit Ray’s detective stories — rarely found in Delhi bookstores. In the English literature section, there were paperbacks stacked with fading spines, vintage hardcovers of Hemmingway, Dickens, Tolstoy, Virginia Woolf, Naipaul and Amitava Ghosh, local publications, books on anything and everything under the sun. I felt like a child in a fantastical forest, each turn revealing new treasures. And also discovered that you have to bargain to get a good discount here. What surprised me most was the atmosphere. Students in uniforms, elderly professors with cloth bags, </t>
+          <t>The security forces on Wednesday achieved a major success in their operation against Maoists as 27 Naxals, including topmost leader Nambala Keshav Rao, aka Basavaraju, were killed in an encounter in the Abujhmad region of Chhattisgarh on the border of Narayanpur and Bijapur districts. A jawan of the Chhattisgarh Police’s District Reserve Guard (DRG) was also killed while a few other personnel sustained injuries in the encounter that had begun several days ago, sources in the state police said. The killing of Keshav Rao, a CPI-Maoist general secretary, has come as a shot in the arm for the security forces as they had recently busted a long-time base of the Naxalites located in Koreguttalu Hills of Bijapur district in Chhattisgarh (bordering Telangana). Thirtyone Naxals were killed and a huge cache of arms, ammunitions and explosives recovered. Four factories where weapons were being manufactured were also unearthed under the three-week-long offensive named Operation Black Forest. Keshav Raocarried a bounty of Rs 1.5 crore and was wanted in connection with several deadly attacks on security forces across multiple states. A native of Jiyyannapet village in Andhra Pradesh's Srikakulam district, he was the son of a school teacher. He studied engineering at Warangal Regional Engineering College (REC) before being drawn into student activism in the 1980s. After being arrested during a student union protest in 1980, he went underground and joined the Naxals. Over the next four decades, Rao rose through the ranks and became known for his meticulous planning, ruthless ambushes, expertise in jungle warfare and making IEDs. Security officials believe he was the mastermind behind the 2010 Dantewada attack, one of the deadliest ever on Indian forces, in which 76 CRPF jawans were killed in Chhattisgarh. Despite the massive bounty, Rao managed to remain elusive for decades. The National Investigation Agency (NIA) had no recent photographs or confirmed details about his age. Prime M</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Business</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1162,22 +1162,22 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2020-06-11</t>
+          <t>2010-04-14</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>https://www.tribuneindia.com/news/nation/punjab-rajasthan-gujarat-put-off-mha-mock-drill/</t>
+          <t>https://www.tribuneindia.com/news/upsc/exam-schedule</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Punjab, Rajasthan, Gujarat put off MHA mock drill</t>
+          <t>Exam Schedule</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Hours after the Ministry of Home Affairs (MHA) ordered to hold mock drills in three states and the UT of J&amp;K bordering Pakistan and Chandigarh on Thursday (May 29), Punjab, Rajasthan, Gujarat and Chandigarh announced to postpone the exercise citing “administrative reasons”. As per orders issued by Rajasthan and Gujarat’s home departments late on Wednesday evening, it was announced that “It is hereby intimated that the Civil Defence Exercise “Operation Shield”, which was planned to be held on May 29 is hereby postponed due to administrative reasons. It is requested that necessary directions to all controllers of civil defence and other stakeholders, may be issued accordingly. Next dates for the exercise shall be issued subsequently”. There was no intimation of postponement of the exercise in J&amp;K. Meanwhile, Haryana, which is not a border state, stated that it would go ahead with the mock drill. Highly placed sources informed that the mock drills will basically test various aspects that were found severely lacking during the May 7 exercise. Serious lacunae were discovered in the civil defence infrastructure, non-functional hotlines, sirens malfunctioned at some places and the lack of training among volunteers was also observed, a top official told The Tribune. Since the past three weeks, the government is aggressively focussing on ramping up the number of civil defence volunteers and also on providing them with specialised training. Even involvement of local people, especially in the border states, will be specially focussed upon, as they are more acclimatised with the conditions and in case of a war-like situation or a natural disaster, when quick response is the need of the hour, they will be of immense help. The Centre also plans to rope in private security agencies, as they have a huge workforce totalling up to more than 1 crore. Talks are currently on to rope in some big players in the field of private security set up, to train their personnel in civil defence pr</t>
+          <t>Exam ScheduleCombined Medical Services Examination, 2025CMS Examination is conducted by the UPSC for recruitment of Medical Officers (Group A posts) to various government departments/organisationsTribune News Service</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
@@ -1200,31 +1200,791 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2020-12-30</t>
+          <t>2010-12-18</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>https://www.tribuneindia.com/news/business/cipla-health-takes-a-humorous-spin-on-real-life-stories-with-astaberrys-campaign-get-the-rich-look-2/</t>
+          <t>https://www.tribuneindia.com/news/sports/sreekala-rani-shines-as-india-beats-tahiti-in-fiba-womens-asia-cup/</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Cipla Health takes a humorous spin on real life stories with Astaberry's campaign 'Get the Rich Look'</t>
+          <t>Sreekala Rani shines as India beats Tahiti in FIBA Women's Asia Cup</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>MUMBAI, India, July 16, 2025 /PRNewswire/ -- Cipla Health, a leading player in the wellness category, announced the launch of Astaberry, its beauty and personal care brand's latest campaign - 'Get the Rich Look'. Rich look stands for the rich texture of skin that glows naturally without the use of any make up or filters thereby boosting confidence in everyday situations. Rooted in nature and designed for the women of Bharat, the campaign celebrates radiant, healthy skin that shines naturally, empowering women to step forward with confidence in every walk of life. Drawing inspiration from real stories shared by our consumers, the film highlights how Astaberry's simple, effective skincare solutions can help women achieve a naturally radiant 'Rich Look'. The film charmingly highlights relatable scenarios with a light-hearted and authentic tone where a subtle beauty upgrade transforms how the world perceives a woman, whether it's meeting someone new, preparing for an important occasion, or stepping into a professional setting. Commenting on the campaign, Mr. Shivam Puri, MD &amp; CEO, Cipla Health Ltd. said, "At Cipla Health, we are committed to bringing solutions that are effective, accessible, and seamlessly fit into the lives of our consumers. This campaign is deeply rooted in real consumer insights and offers a refreshing take on the quiet confidence that naturally radiant skin brings. Astaberry has always stood for nature-powered skincare that is reliable, affordable, and designed for all skin types. As the beauty and personal care market expands rapidly, especially beyond metros, this film reinforces our commitment to offering trusted solutions that meet the evolving aspirations of women across India." Astaberry*, with a legacy of over 16 years, offers a comprehensive skincare portfolio across more than 10 categories and 250+ products. From hair removal creams and face washes to serums, sun protection, and facial kits, each product is infused with nature-based ingredi</t>
+          <t>Shenzhen [China], July 16 (ANI): The Indian basketball team marched into the semi-final qualifiers at the FIBA Women's Asia Cup 2025 Division B after beating Tahiti 78-55 in its final Group A match here on Wednesday. Sreekala Rani, with 15 points, six rebounds and five assists, was India's top performer in the match played at the Shenzhen Bay Sports Centre, as per Olympics.com. Moina Michelle Tuieinui-Le Beherec (15 points and 10 rebounds) managed a double and was Tahiti's standout player in the contest. Sreekala Rani opened the scoring with a two-point layup, but India, world No. 15 in the FIBA basketball rankings, failed to exert their dominance in the early exchanges as the unranked Tahiti went toe-to-toe. However, with the score reading 15-12, the script changed. India scored 10 unanswered points after that and took a 25-13 lead at the opening quarter hooter. The Indian team extended its lead to 46-25 at half-time before a fairly even third period saw the score at 61-40. India. However, edged the final quarter to drive home the win. Courtesy of the victory, India also finished second in Group A with five points, one behind Chinese Taipei, who defeated Kazakhstan 91-47 earlier in the day to seal the top spot and a direct entry into the semi-finals. The Indian basketball team, meanwhile, will face the third-placed team from Group B in the FIBA Women's Asia Cup 2025 Division B semi-final qualifiers on Friday. India is returning to the FIBA Women's Asia Cup fold after a four-year absence. They missed the 2023 edition following their relegation from Division A in 2021 and are now competing in Division B at this year's continental championship. A total of eight teams, divided into two groups, are competing in Division B of the 31st FIBA Women's Asia Cup. India were drawn in Group A with Kazakhstan, Chinese Taipei and Tahiti. After round robin matches, the two group toppers qualify directly for the semi-finals. Meanwhile, the second and third-placed teams from each gro</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>NOT_SUMMARIZED</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>The Tribune</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2011-06-27</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>https://www.tribuneindia.com/news/premium/inclusive-approach-a-must-to-study-inequality-in-india/</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Inclusive approach a must to study inequality in India</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>A World Bank report has claimed a drastic reduction in the state of inequality in India between 2011 and 2022. While it is a valuable tool for aligning India’s metrics with global targets, the report predominantly emphasises administrative progress in aggregated outcomes, missing ground-level disparities in access, affordability and inclusion. Take your experience further with Premium access.Thought-provoking Opinions, Expert Analysis, In-depth Insights and other Member Only Benefits The Tribune, now published from Chandigarh, started publication on February 2, 1881, in Lahore (now in Pakistan). It was started by Sardar Dyal Singh Majithia, a public-spirited philanthropist, and is run by a trust comprising five eminent persons as trustees.The Tribune, the largest selling English daily in North India, publishes news and views without any bias or prejudice of any kind. Restraint and moderation, rather than agitational language and partisanship, are the hallmarks of the newspaper. It is an independent newspaper in the real sense of the term.The Tribune has two sister publications, Punjabi Tribune (in Punjabi) and Dainik Tribune (in Hindi). Remembering Sardar Dyal Singh Majithia</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>NOT_SUMMARIZED</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>The Tribune</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2012-06-26</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>https://www.tribuneindia.com/news/nation/sc-asks-assam-human-rights-panel-to-probe-police-encounters/</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>SC asks Assam human rights panel to probe police encounters</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>The Supreme Court on Wednesday directed the Assam Human Rights Commission (AHRC) to conduct an independent probe into over 171 police encounters that took place in the state between May 2021 and August 2022, in which proper procedure was allegedly not followed. “We entrust this matter to the Assam Human Rights Commission for necessary enquiry, independently and expeditiously. It must be ensured that victims and family members are given a fair opportunity,” a Bench of Justice Surya Kant and Justice N Kotiswar Singh said. It directed the AHRC, headed by a retired HC chief justice, to issue a public notice inviting claims of the aggrieved, while ensuring confidentiality. The Bench said a blanket direction based on a mere compilation of cases was not justified even as it noted that a few specific instances might warrant further evaluation. The top court issued these directions while disposing of a petition filed by Arif Md Yeasin Jwadder alleging fake encounters by the Assam Police. He had sought an independent investigation into more than 171 police encounters in the state. The Bench concluded that most of the instances of alleged non-compliance with procedural guidelines, laid down by the top court in 2014, highlighted by the petitioner appeared to be factually incorrect. Barring a few of the cases, it was difficult to conclude that there were flagrant violations of guidelines, the top court said. It granted liberty to the AHRC to initiate further investigations into the allegations of fake encounters and asked the Assam Government to extend cooperation and remove any institutional barriers in the inquiry process. It asked the AHRC to safeguard the privacy of the complainants and approach the matter with sensitivity. It directed the Assam State Legal Services Authority to provide legal aid to the kin of victims of alleged fake encounters. The Assam Government has contended that the 2014 guidelines for investigating police encounters were duly followed in the state and</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Politics</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>NOT_SUMMARIZED</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>The Tribune</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2012-10-08</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>https://www.tribuneindia.com/news/shaharnama/bicycle-rides-on-brahmaputras-banks-in-dibrugarh/</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Bicycle rides on Brahmaputra’s banks in Dibrugarh</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Some memories never fade away — of places, of people and neighbourhoods, and remain as fresh and vivid as if they happened yesterday. My visits to Dibrugarh, Assam, on the banks of Brahmaputra, famous for its vast tea plantations, are part of such memories. My parents took me and my sibling to this quaint town during our summer holidays to our grandparents’ home. They lived in a place called Tinkunia, very close to the embankment of the Brahmaputra river. During the visits, we would routinely go for strolls along the embankment. The views of the Brahmaputra river flowing majestically and the stunning landscape dotted with trees and a row of colonial buildings-turned-offices and courts used to be breath-taking. There was a rickety wooden pier extending to the river and we used to tread carefully, lest our chappals got stuck in the gaps in between the wooden planks. I also learnt how to ride a bicycle, falling and tripping, ripping my knees so many times. I would frequent Graham Bazaar on bicycle with my uncle, where we would relish dosas, rounding it off with the special meetha paan from the famous Sukhlal paan dukan. I also loved to visit the lush tea gardens dotting the town and also the sprawling campus of Assam Medical College &amp; Hospital. I drive other vehicles now but the memories of my childhood days and maiden cycle rides in Dibrugarh often flash in my mind. Take your experience further with Premium access.Thought-provoking Opinions, Expert Analysis, In-depth Insights and other Member Only Benefits The Tribune, now published from Chandigarh, started publication on February 2, 1881, in Lahore (now in Pakistan). It was started by Sardar Dyal Singh Majithia, a public-spirited philanthropist, and is run by a trust comprising five eminent persons as trustees.The Tribune, the largest selling English daily in North India, publishes news and views without any bias or prejudice of any kind. Restraint and moderation, rather than agitational language and partisanship, ar</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>NOT_SUMMARIZED</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>The Tribune</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2013-05-13</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>https://www.tribuneindia.com/news/nation/rural-health-officer-shot-in-patna/</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Rural health officer shot in Patna</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>A 50-year-old rural health officer was shot dead in Patna’s Pipra locality, officials said on Sunday. The deceased has been identified as Surendra Kumar. The incident occurred on Saturday night in Sheikhpura village while Kumar was working in a field. “According to villagers, they heard gunshots from the field, and when they rushed there, the officer was found lying unconscious with bullet injuries,” said Masaurhi Sub-Divisional Police Officer Kanhaiya Singh. Kumar, reportedly associated with the BJP, was taken to a nearby hospital where he succumbed to his injuries during treatment, Singh added. The body has been sent for post-mortem examination and an investigation is underway. The killing comes amid a spate of violent crimes in the Bihar capital over the past week. On July 10, a man linked to the sand mining trade was shot dead outside his home in Ranitalab. On July 4, prominent industrialist Gopal Khemka was murdered in Patna, sparking widespread public and political outrage. Take your experience further with Premium access.Thought-provoking Opinions, Expert Analysis, In-depth Insights and other Member Only Benefits The Tribune, now published from Chandigarh, started publication on February 2, 1881, in Lahore (now in Pakistan). It was started by Sardar Dyal Singh Majithia, a public-spirited philanthropist, and is run by a trust comprising five eminent persons as trustees.The Tribune, the largest selling English daily in North India, publishes news and views without any bias or prejudice of any kind. Restraint and moderation, rather than agitational language and partisanship, are the hallmarks of the newspaper. It is an independent newspaper in the real sense of the term.The Tribune has two sister publications, Punjabi Tribune (in Punjabi) and Dainik Tribune (in Hindi). Remembering Sardar Dyal Singh Majithia</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Politics</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>NOT_SUMMARIZED</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>The Tribune</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2013-05-14</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>https://www.tribuneindia.com/news/entertainment/syrian-designer-rami-al-alis-paris-debut/</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Syrian designer Rami Al Ali’s Paris debut</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Syrian designer Rami Al Ali made history as the first Syrian featured on the official calendar of Paris Haute Couture Week, showcasing his collection Guardian of Light. Known for its soft pastels, silk and crepe fabrics, and detailed embroidery, the collection symbolizes hope and renewal amid Syria’s political changes. Based in Dubai, Al Ali called the moment a proud milestone for both his career and Syrian fashion. With past clients like Beyoncé and Helen Mirren, this recognition solidifies his global impact. He believes Syrian creatives now have more freedom to express their identity and culture. Take your experience further with Premium access.Thought-provoking Opinions, Expert Analysis, In-depth Insights and other Member Only Benefits The Tribune, now published from Chandigarh, started publication on February 2, 1881, in Lahore (now in Pakistan). It was started by Sardar Dyal Singh Majithia, a public-spirited philanthropist, and is run by a trust comprising five eminent persons as trustees.The Tribune, the largest selling English daily in North India, publishes news and views without any bias or prejudice of any kind. Restraint and moderation, rather than agitational language and partisanship, are the hallmarks of the newspaper. It is an independent newspaper in the real sense of the term.The Tribune has two sister publications, Punjabi Tribune (in Punjabi) and Dainik Tribune (in Hindi). Remembering Sardar Dyal Singh Majithia</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>NOT_SUMMARIZED</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>The Tribune</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2013-09-26</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>https://www.tribuneindia.com/news/reflections/its-bombay-its-mumbai-its-home/</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>It’s Bombay, it’s Mumbai, it’s home</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>I moved to Mumbai when I was nine. A Pahadi girl in hand-me-down sweaters with a Hindi-English tongue. I landed in the city fast asleep on a red-eye Air India flight, clutching my mother’s sari like it was the last familiar thing I had. As the kaali-peeli curved past the streets at dawn, the first sight that stirred me awake was the Haji Ali Dargah — bathed in sunrise, floating on the Arabian Sea, shimmering like a promise. I didn’t know the language. I didn’t know the map. But in that moment, I knew: I was home. I was a Mumbaikar. We came here not by design, but by transfer. My parents were in government service, and we hopped from town to town, state to state, enough that I knew never to get too attached to a pincode or a school. Marathi wasn’t taught in our home, wasn’t part of my curriculum, and wasn’t mandatory. And yet, after three decades of living here, I’m told by politicians, by Twitter eggs, by MNS banners that I’m not a “true” Mumbaikar because I don’t speak Marathi. Mumbai — or Bombay, depending on what the soul calls it — is a city of many migrations and many contradictions. It’s the city of Shobhaa De’s English, Amrita Fadnavis’ Marathi, Haji Ali’s Urdu, Lalbaug’s Marathi-Portuguese dialect, Dharavi’s Tamil, Malad’s Gujarati, Bandra’s Catholic Konkani, and Lokhandwala’s version of what we’ll generously call Punjabi. This city hears over 20 languages spoken every single day. It welcomes everyone and no one in equal measure. The recent Marathi language controversy spearheaded by MNS isn’t about preserving culture — it’s about posturing. When the economy is faltering, governance is chaotic, and Mumbai is flooding yet again, linguistic nationalism becomes the perfect decoy. It allows leaders to manufacture offence, to invent a threat where none exists, and to position themselves as protectors of identity, without having to do the hard work of actual governance. I say this not as a political pundit, but as someone who’s walked these streets for 30 years. I</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Politics</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>NOT_SUMMARIZED</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>The Tribune</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2014-06-24</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>https://www.tribuneindia.com/news/premium/not-just-water-its-debris-that-is-drowning-himachal-pradesh/</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Not just water, it’s debris that is drowning Himachal Pradesh</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>For the third consecutive year, Himachal Pradesh finds itself reeling under the fury of the monsoon. Here’s something that often gets missed: one striking commonality in rain-induced tragedies in the past three consecutive years has been the dominance of the flow of debris. It is not just water but massive volumes of muck, boulders, tree trunks and landslide material that are sweeping away roads, homes, bridges, villages and entire markets when all of it comes crashing down with the rainwater. Take your experience further with Premium access.Thought-provoking Opinions, Expert Analysis, In-depth Insights and other Member Only Benefits The Tribune, now published from Chandigarh, started publication on February 2, 1881, in Lahore (now in Pakistan). It was started by Sardar Dyal Singh Majithia, a public-spirited philanthropist, and is run by a trust comprising five eminent persons as trustees.The Tribune, the largest selling English daily in North India, publishes news and views without any bias or prejudice of any kind. Restraint and moderation, rather than agitational language and partisanship, are the hallmarks of the newspaper. It is an independent newspaper in the real sense of the term.The Tribune has two sister publications, Punjabi Tribune (in Punjabi) and Dainik Tribune (in Hindi). Remembering Sardar Dyal Singh Majithia</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
           <t>Business</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>NOT_SUMMARIZED</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>The Tribune</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2014-06-26</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>https://www.tribuneindia.com/news/sports/a-little-disappointed-sourav-ganguly-following-indias-loss-at-lords-to-england/</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>"A little disappointed": Sourav Ganguly following India's loss at Lord's to England</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Mumbai (Maharashtra) [India], July 16 (ANI): Following India's loss at Lord's during the third Test against England, former India captain Sourav Ganguly shared his feelings on the game, where he said that he felt a "little disappointed" with the result as he thought that India should have chased down a mere total of 193 as they have batted so well in the series so far. An unfortunate dismissal of Mohammed Siraj at the hands of Shoaib Bashir, with the ball rolling back into the stumps after a landing on the pitch, marked the end of India's stubborn resistance at Lord's, with Ravindra Jadeja left stranded following a heartbreaking 22-run loss. India lost the match despite dominating England for large parts of the game, with one of the standout performers being Jasprit Bumrah. He took seven wickets, including a five-wicket haul in the first innings. Speaking on India's narrow defeat against England at Lord's, Ganguly said, "I am a little bit disappointed because the way India batted in this series so far, they should have got this one...The batting quality in this team is absolutely brilliant. I think they will be more disappointed than I am..." Coming to the match, England won the toss and opted to bat first. England was reduced to 44/2, but a 109-run stand between Ollie Pope (44 in 104 balls, with four boundaries) and Joe Root (104 in 199 balls, with 10 fours) and a counter-attacking 84 run stand for the eighth wicket stand between Brydon Carse (56 in 83 balls, with six fours and a six) and Jamie Smith (51 in 56 balls, with six fours) took England to 387. Jasprit Bumrah (5/74) was the highlight for India with the ball. In the second innings, India lost Yashasvi Jaiswal early, but a 61-run stand between Karun Nair (26 in 46 balls, with five fours) and KL Rahul and a 141-run stand between KL (100 in 177 balls, with 13 fours) and Rishabh Pant (74 in 112 balls, with eight fours and two sixes) took India close to England's score. A brilliant half-century from Ravindra Jad</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>NOT_SUMMARIZED</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>The Tribune</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2015-06-24</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>https://www.tribuneindia.com/news/remembering-bn-goswamy/</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Remembering B N Goswamy</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Remembering B N GoswamyThe world of craftswomenI haven’t read it myself, but someone narrated to me a story by U.R. Anantamurthy once in which the writer speaks feelingly about the two very different worlds inhabited by men and women of the same family in a traditional, well-to-do...B.N. Goswamy</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>General News</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>NOT_SUMMARIZED</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>The Tribune</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2015-11-14</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>https://www.tribuneindia.com/news/diaspora/sikh-mp-dhesi-says-afghan-nationals-at-risk-slams-uk-govt-over-data-leak/</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>British MP Tanmanjeet Dhesi says 'Afghan nationals at risk', slams UK govt over data leak</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>British MP Tanmanjeet Singh Dhesi, Chair of Parliament’s Defence Select Committee, has strongly criticised the UK government over its handling of a sensitive data breach that exposed thousands of Afghan nationals to potential danger. In an interview with Times Radio following the lifting of a long-standing court gag order, Dhesi described the situation as “an absolute mess and wholly unacceptable.” “It’s shameful that those Afghans who bravely supported our service personnel are now at risk,” he said. “I am minded to launch a committee investigation.” Dhesi, a senior Labour MP representing Slough, a diverse town west of London, was elected in 2017 as the UK’s first turbaned Sikh parliamentarian. Before entering national politics, he served as mayor of Gravesend, a historic riverside town in Kent with a sizeable South Asian population. The incident stems from a 2022 error by a Ministry of Defence (MoD) official, who mistakenly sent a spreadsheet containing the personal details of more than 33,000 Afghan citizens applying for resettlement in the UK under the Afghan Relocations and Assistance Policy (ARAP). Many of those listed had worked alongside British troops during the war. In an effort to contain the fallout, the government secured a superinjunction in September 2023 — a rarely used legal tool that barred any mention of the case, even its existence. That order was lifted earlier this week following a prolonged legal challenge by The Times and other British media outlets. Delivering his judgment last Tuesday, Justice Chamberlain warned that the sweeping secrecy created a “scrutiny vacuum” and “shut down the ordinary mechanisms of accountability which operate in a democracy.” In the House of Commons on Tuesday, UK Defence Secretary John Healey acknowledged the government’s mishandling of the issue: “I feel deeply uncomfortable about what happened. I apologize on behalf of the government to those affected.” An independent review, commissioned by a former senior civi</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Politics</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>NOT_SUMMARIZED</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>The Tribune</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2016-02-21</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>https://www.tribuneindia.com/news/business/amdark-limited-launches-comprehensive-investment-fraud-recovery-program-to-combat-online-scam/</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Amdark Limited Launches Comprehensive Investment Fraud Recovery Program to Combat online Scam</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>New Delhi [India], July 16: Amdark Limited, a global leader in financial recovery and digital forensic services, today introduced its expanded Investment Fraud Recovery Program, designed to help victims of online scams--including cryptocurrency, forex, binary options, Ponzi schemes, and phishing attacks--reclaim lost funds and secure legal redress. Rising Threat of Online Investment Scams Digital investment fraud is escalating dramatically. From deceptive crypto scams to high-pressure forex and binary trading schemes, victims face significant financial losses and limited recovery options. As noted by GlobeNewswire, "online scams have become a significant concern in the digital finance space," targeting both novice and institutional investors. Due to the irreversible nature of cryptocurrency transactions, many victims find themselves stranded, often unable to trace stolen funds through conventional banking systems. Amdark Limited: Expertise in Forensics and Legal Advocacy Amdark Limited specializes in asset recovery through a unique combination of blockchain forensics, legal strategy, and global collaboration. Their comprehensive approach includes: * Advanced Forensic Technology: Cutting-edge tools trace digital asset flows across multiple environments, even when criminals use obfuscation tactics. * Global Legal Network: Amdark's team of forensic experts and international lawyers ensures victims receive jurisdictional legal support, from filing complaints to asset freezes. * Tailored Case Management: Through thorough case evaluation--from wallet address collection to communication correspondence--Amdark delivers personalized recovery strategies . "We empower victims by combining forensic precision with legal acumen, offering them the best chance to recover and seek justice," said Alan Kalbfell, spokesperson for Amdark Limited. Aligned with this year's surge in digital fraud, Amdark Limited has significantly broadened its service portfolio: Handling cases from phishin</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Business</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>NOT_SUMMARIZED</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>The Tribune</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2016-11-16</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>https://www.tribuneindia.com/news/world/madhya-pradesh-govt-committed-to-providing-best-facilities-to-youth-interested-in-football-mp-cm-mohan-yadav/</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>"Madhya Pradesh govt committed to providing best facilities to youth interested in football": MP CM Mohan Yadav</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Madrid [Spain], July 16 (ANI): Madhya Pradesh Chief Minister Dr Mohan Yadav on Wednesday visited the headquarters of Spain's top football league, La Liga, in Madrid and reiterated the state government's commitment to enhancing sports infrastructure, especially for the youth interested in football. During his visit, Yadav met senior La Liga officials and discussed potential avenues of cooperation in the areas of sports development and youth training. Speaking to ANI, the Madhya Pradesh Chief Minister said, "I visited the La Liga office where players from different countries play and young talents are nurtured by providing good training and facilities... La Liga is playing a huge role in promoting football." Highlighting that La Liga has signed an MoU with both the Union and the State Government, CM Yadav underscored, "The Madhya Pradesh government is committed to providing the best facilities to the youth interested in playing football so that they can bring laurels to the country in sports." The visit to La Liga was part of CM Yadav's ongoing official tour to Spain, which is focused on attracting global investment, encouraging technology exchange, and generating employment opportunities under the "Global Dialogue 2025" initiative. Yadav is currently on the second leg of his two-nation tour. He reached the Spanish capital after completing a three-day visit to the United Arab Emirates on Tuesday. According to a post on X by the Madhya Pradesh Chief Minister's Office (CMO), Yadav met senior La Liga officials and discussed possible cooperation in sports and youth development. The discussions covered a range of topics, including infrastructure support, grassroots development, and football training. "Chief Minister Dr. Mohan Yadav, during his visit to Madrid, Spain, visited the La Liga office and held discussions with senior officials to explore collaboration in sports and youth development. The discussions focused on football training, grassroots development, and infrast</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Politics</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>NOT_SUMMARIZED</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>The Tribune</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2017-03-08</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>https://www.tribuneindia.com/news/sports/j-k-martial-arts-gain-popularity-among-youth-in-kashmir-valley/</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>J-K: Martial arts gain popularity among youth in Kashmir valley</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Srinagar (Jammu and Kashmir) [India], July 16 (ANI): Martial arts are becoming more popular among young people in the Kashmir valley, with regular tournaments and championships attracting a growing number of participants. This rising interest shows that many students now see martial arts not just as a hobby but also as a possible career path. Many youngsters are joining martial arts training programmes to learn self-defence and to improve their physical and mental health. Coaches across the region are using this interest to organise more competitions, which help train young athletes and give them a chance to perform. "Sports, especially martial arts, help students manage the stress caused by academic pressures and career aspirations. Parents are now actively encouraging both boys and girls to participate, seeing the long-term benefits in terms of discipline, fitness, and confidence," local coach Mansha Bashir told ANI. These events, mostly organised by local sports associations, give children a chance to train and compete. Many of the participants are in their early teens, and the strong response has led to calls for more such events in future. Young participants have also asked for continued support and more chances to take part in martial arts. They believe regular events and training will help the sport grow across the valley. With rising interest and strong community support, martial arts are slowly becoming a mainstream sport in the Kashmir valley, helping young people stay healthy and focused. (ANI) (This content is sourced from a syndicated feed and is published as received. The Tribune assumes no responsibility or liability for its accuracy, completeness, or content.) Take your experience further with Premium access.Thought-provoking Opinions, Expert Analysis, In-depth Insights and other Member Only Benefits The Tribune, now published from Chandigarh, started publication on February 2, 1881, in Lahore (now in Pakistan). It was started by Sardar Dyal Singh Ma</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>NOT_SUMMARIZED</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>The Tribune</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2018-05-26</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>https://www.tribuneindia.com/news/entertainment/dhanushs-kuberaa-set-for-ott-debut/</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Dhanush's Kuberaa set for OTT debut</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Actor Dhanush’s latest film Kuberaa is set to premiere on Prime Video on 18 July, the streaming platform announced on Friday, following its theatrical release last month. Directed by National Award-winning filmmaker Sekhar Kammula, known for Dollar Dreams, Anand and Happy Days, Kuberaa is a pan-Indian political thriller featuring an ensemble cast that includes Telugu superstar Nagarjuna, Rashmika Mandanna, Jim Sarbh and Dalip Tahil. The film, which hit cinemas on 20 June, will be available in five languages — Tamil, Telugu, Hindi, Kannada and Malayalam. The story centres on Deva (Dhanush), a modest drifter from Tirupati who finds himself caught in a dangerous web of deceit and ambition. His life spirals into chaos when corporate tycoon Neeraj Mithra (Sarbh) discovers a secret oil reserve and manipulates a disgraced former CBI officer, Deepak Tej (Nagarjuna), into helping him seize it. Take your experience further with Premium access.Thought-provoking Opinions, Expert Analysis, In-depth Insights and other Member Only Benefits The Tribune, now published from Chandigarh, started publication on February 2, 1881, in Lahore (now in Pakistan). It was started by Sardar Dyal Singh Majithia, a public-spirited philanthropist, and is run by a trust comprising five eminent persons as trustees.The Tribune, the largest selling English daily in North India, publishes news and views without any bias or prejudice of any kind. Restraint and moderation, rather than agitational language and partisanship, are the hallmarks of the newspaper. It is an independent newspaper in the real sense of the term.The Tribune has two sister publications, Punjabi Tribune (in Punjabi) and Dainik Tribune (in Hindi). Remembering Sardar Dyal Singh Majithia</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>NOT_SUMMARIZED</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>The Tribune</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2018-06-08</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>https://www.tribuneindia.com/news/shaharnama/the-joys-of-visiting-the-city-of-joy/</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>The joys of visiting the City of Joy</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>I first visited Kolkata as a child when my father took us to the City of Joy during school holidays in the early 80s. I remember the long train journey from our hometown, Guwahati. We would often visit the famous Victoria Memorial, and go around the surrounding green sprawling Maidan on horse-drawn buggies. For going around the city, we would use its iconic yellow taxis to see its other famous landmarks like the Howrah Bridge, Vidyasagar Setu and other imposing colonial-era buildings on the banks of Hooghly. It was the only metropolis with tram services and we loved hopping onto the slow-moving electric trams that navigated its busy streets alongside other vehicles. We also enjoyed travelling the Metro there, which was the country's first metro service. Most of our evenings were spent frequenting the Esplanade and the Chowringhee for shopping, and savouring the street food there, as well as gorging on a wide variety of mishti (sweets) and faluda. Chinatown (Tiriti Bazaar) was another of our favourite destinations. Kolkata remains the only place where you can still find hand-pulled rickshaws plying in its alleys and by-lanes. As a kid I enjoyed riding in these rickshaws. I also have fond memories of New Year celebrations in the famous Park Street during later visits. Even now Kolkata never fails to fascinate me. Every time I visit, it still has more surprises offer. Take your experience further with Premium access.Thought-provoking Opinions, Expert Analysis, In-depth Insights and other Member Only Benefits The Tribune, now published from Chandigarh, started publication on February 2, 1881, in Lahore (now in Pakistan). It was started by Sardar Dyal Singh Majithia, a public-spirited philanthropist, and is run by a trust comprising five eminent persons as trustees.The Tribune, the largest selling English daily in North India, publishes news and views without any bias or prejudice of any kind. Restraint and moderation, rather than agitational language and partisanship, a</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>NOT_SUMMARIZED</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>The Tribune</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2018-07-08</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>https://www.tribuneindia.com/news/world/mp-cm-mohan-yadav-visits-la-liga-hq-in-madrid-discusses-sports-collaboration/</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>MP CM Mohan Yadav visits La Liga HQ in Madrid, discusses sports collaboration</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Madrid [Spain], July 16 (ANI): Madhya Pradesh Chief Minister Mohan Yadav on Wednesday visited the headquarters of Spain's top football league, La Liga, in Madrid. The visit was part of his official tour to Spain, aimed at attracting global investment to the state, encouraging technology exchange, and creating jobs under the "Global Dialogue 2025" initiative. Yadav is currently on the second leg of his two-nation tour. He reached the Spanish capital after completing a three-day visit to the United Arab Emirates on Tuesday. According to a post on X by the Madhya Pradesh Chief Minister's Office (CMO), Yadav met senior La Liga officials and discussed possible cooperation in sports and youth development. The discussions covered a range of topics, including infrastructure support, grassroots development, and football training. "Hon'ble Chief Minister Dr. Mohan Yadav, during his visit to Madrid, Spain, visited the LaLiga office and held discussions with senior officials to explore collaboration in sports and youth development. The discussions focused on football training, grassroots development, and infrastructure support in Madhya Pradesh. This visit reflects the state's vision to empower youth through global sports partnerships," The MP CMO stated on X. Yadav will remain in Spain until July 19. During his stay, he is scheduled to hold bilateral meetings with India's Ambassador to Spain, Dinesh K Patnaik, and explore business and investment opportunities in Madhya Pradesh. He will also take part in a leadership dialogue, interact with business forums in Madrid and Barcelona, meet members of the Indian community, and go on an industry tour. Earlier in the day, Yadav arrived in Madrid, leading a high-level delegation as part of his official visit to Spain. Yadav and his delegation were received at the Madrid Barajas Airport by India's Ambassador to Spain, Dinesh K Patnaik. Sharing the pictures of the MP CM's arrival, the Indian embassy in Spain wrote, "High-level delegation</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Politics</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>NOT_SUMMARIZED</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>The Tribune</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2018-12-26</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>https://www.tribuneindia.com/news/world/indonesias-11-year-old-aura-farmer-dikha-wins-hearts-then-scholarship-government-title/</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Indonesia’s 11-year-old ‘aura farmer’ Dikha wins hearts, then scholarship, government title</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>The boat-dancing kid, Rayyan Arkan Dikha, has become internet’s favourite since a video of him dancing on the tip of a boat during the Pacu Jalur boat race in Riau province of Indonesia, went viral. diego luna really hit that 😂 pic.twitter.com/AC69ec8y3U — Major League Soccer (@MLS) July 2, 2025 Dikha’s traditional outfit, slick sunglasses, calm expression and hypnotic moves have made him an overnight global sensation who’s been dubbed the ultimate ‘aura farmer’ by the internet. Now, his hometown is giving him his flowers. According to reports by Hindustan Times, the government of Riau named Dika a tourism ambassador last week, celebrating his role in reviving culture among local kids. Governor Abdul Wahid also rewarded the 11-year-old a scholarship worth 20 million rupiah (around $1,200 USD). The official ceremony featured Dikha doing what he does best – dancing, this time alongside the governor himself. Also read: ‘Came up with it myself’: Indonesian boy’s dance on boat goes viral, inspires Travis Kelce “Wow, I am so happy,” Dika said in Indonesian in the government’s official announcement. “I never imagined I would meet the governor.” Dika has not just danced for fun, he served as a Tukang Tari, or dancer, whose job is to energise the rowers during the Pacu Jalur races. He’s been doing this since he was 9 years old, but this year, his performance resonated globally. Take your experience further with Premium access.Thought-provoking Opinions, Expert Analysis, In-depth Insights and other Member Only Benefits The Tribune, now published from Chandigarh, started publication on February 2, 1881, in Lahore (now in Pakistan). It was started by Sardar Dyal Singh Majithia, a public-spirited philanthropist, and is run by a trust comprising five eminent persons as trustees.The Tribune, the largest selling English daily in North India, publishes news and views without any bias or prejudice of any kind. Restraint and moderation, rather than agitational language and partisanshi</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Politics</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>NOT_SUMMARIZED</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>The Tribune</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2019-04-30</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>https://www.tribuneindia.com/news/delhi/on-a-literary-pilgrimage-to-kolkatas-college-street/</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>On a literary pilgrimage to Kolkata’s College Street</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">As someone who hails from Delhi, a city bustling with political discourse and historical gravitas, the idea of visiting Kolkata’s College Street had long fascinated me. Called Boi Para (book town) locally, it is more than just a marketplace; it is a cultural phenomenon. On a crisp winter morning, I boarded a flight to Kolkata with only one purpose: to spend a full day in the legendary book haven. College Street was unlike anything I had experienced in Delhi. While the Sunday book bazaar in Mahila Haat near Delhi Gate has its own charm, there was no beating the raw intellectual energy that coursed through College Street. As soon as I arrived in this largest book market in India and the largest second-hand book market in the world, I was struck by the sheer density of bookstalls—hundreds of them, stretching endlessly on both sides of the road, manned by sellers who knew the exact location of any book — be it a rare Bengali translation of Dostoevsky or a weathered copy of Malgudi Days or Mulk Raj Anand’s Coolie, without even looking. People of all ages didn’t just buy books — they argued about them, recommended them to strangers, and flipped through pages with a reverence. I began my exploration with Bengali classics — Rabindranath Tagore’s famous Ghare Baire (The Home and the World), Sarat Chandra Chattopadhyay’s Srikanta, and Bibhutibhushan Bandyopadhyay’s Pather Panchali. I also picked up a collection of Satyajit Ray’s detective stories — rarely found in Delhi bookstores. In the English literature section, there were paperbacks stacked with fading spines, vintage hardcovers of Hemmingway, Dickens, Tolstoy, Virginia Woolf, Naipaul and Amitava Ghosh, local publications, books on anything and everything under the sun. I felt like a child in a fantastical forest, each turn revealing new treasures. And also discovered that you have to bargain to get a good discount here. What surprised me most was the atmosphere. Students in uniforms, elderly professors with cloth bags, </t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Business</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>NOT_SUMMARIZED</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>The Tribune</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2020-06-11</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>https://www.tribuneindia.com/news/nation/punjab-rajasthan-gujarat-put-off-mha-mock-drill/</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Punjab, Rajasthan, Gujarat put off MHA mock drill</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Hours after the Ministry of Home Affairs (MHA) ordered to hold mock drills in three states and the UT of J&amp;K bordering Pakistan and Chandigarh on Thursday (May 29), Punjab, Rajasthan, Gujarat and Chandigarh announced to postpone the exercise citing “administrative reasons”. As per orders issued by Rajasthan and Gujarat’s home departments late on Wednesday evening, it was announced that “It is hereby intimated that the Civil Defence Exercise “Operation Shield”, which was planned to be held on May 29 is hereby postponed due to administrative reasons. It is requested that necessary directions to all controllers of civil defence and other stakeholders, may be issued accordingly. Next dates for the exercise shall be issued subsequently”. There was no intimation of postponement of the exercise in J&amp;K. Meanwhile, Haryana, which is not a border state, stated that it would go ahead with the mock drill. Highly placed sources informed that the mock drills will basically test various aspects that were found severely lacking during the May 7 exercise. Serious lacunae were discovered in the civil defence infrastructure, non-functional hotlines, sirens malfunctioned at some places and the lack of training among volunteers was also observed, a top official told The Tribune. Since the past three weeks, the government is aggressively focussing on ramping up the number of civil defence volunteers and also on providing them with specialised training. Even involvement of local people, especially in the border states, will be specially focussed upon, as they are more acclimatised with the conditions and in case of a war-like situation or a natural disaster, when quick response is the need of the hour, they will be of immense help. The Centre also plans to rope in private security agencies, as they have a huge workforce totalling up to more than 1 crore. Talks are currently on to rope in some big players in the field of private security set up, to train their personnel in civil defence pr</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Politics</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>NOT_SUMMARIZED</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>The Tribune</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2020-12-30</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>https://www.tribuneindia.com/news/business/cipla-health-takes-a-humorous-spin-on-real-life-stories-with-astaberrys-campaign-get-the-rich-look-2/</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Cipla Health takes a humorous spin on real life stories with Astaberry's campaign 'Get the Rich Look'</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>MUMBAI, India, July 16, 2025 /PRNewswire/ -- Cipla Health, a leading player in the wellness category, announced the launch of Astaberry, its beauty and personal care brand's latest campaign - 'Get the Rich Look'. Rich look stands for the rich texture of skin that glows naturally without the use of any make up or filters thereby boosting confidence in everyday situations. Rooted in nature and designed for the women of Bharat, the campaign celebrates radiant, healthy skin that shines naturally, empowering women to step forward with confidence in every walk of life. Drawing inspiration from real stories shared by our consumers, the film highlights how Astaberry's simple, effective skincare solutions can help women achieve a naturally radiant 'Rich Look'. The film charmingly highlights relatable scenarios with a light-hearted and authentic tone where a subtle beauty upgrade transforms how the world perceives a woman, whether it's meeting someone new, preparing for an important occasion, or stepping into a professional setting. Commenting on the campaign, Mr. Shivam Puri, MD &amp; CEO, Cipla Health Ltd. said, "At Cipla Health, we are committed to bringing solutions that are effective, accessible, and seamlessly fit into the lives of our consumers. This campaign is deeply rooted in real consumer insights and offers a refreshing take on the quiet confidence that naturally radiant skin brings. Astaberry has always stood for nature-powered skincare that is reliable, affordable, and designed for all skin types. As the beauty and personal care market expands rapidly, especially beyond metros, this film reinforces our commitment to offering trusted solutions that meet the evolving aspirations of women across India." Astaberry*, with a legacy of over 16 years, offers a comprehensive skincare portfolio across more than 10 categories and 250+ products. From hair removal creams and face washes to serums, sun protection, and facial kits, each product is infused with nature-based ingredi</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Business</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
         <is>
           <t>NOT_SUMMARIZED</t>
         </is>

--- a/new_excel.xlsx
+++ b/new_excel.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H41"/>
+  <dimension ref="A1:I41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,6 +469,11 @@
           <t>Summary Status</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>AI Summary</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -504,7 +509,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>NOT_SUMMARIZED</t>
+          <t>SUMMARIZED</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>The Shiromani Akal Dal’s revival is facing challenges as evidenced by the significant exodus of leaders, particularly in the Doaba region. Protests recently held yielded a small number of recognizable faces, indicating a decline in the party’s popularity. This suggests a serious struggle for the Akal Dal to regain its former influence.</t>
         </is>
       </c>
     </row>
@@ -542,7 +552,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>NOT_SUMMARIZED</t>
+          <t>SUMMARIZED</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Mrunal Thakur revealed that “Son of Sardaar 2” marked her first foray into commercial entertainment, thanks to encouragement from Ajay Devgn. The film, a sequel to the 2012 hit, features Thakur playing a comedic role alongside Devgn and a large ensemble cast, including those who fondly remember co-star Mukul Dev. Thakur expressed gratitude for the opportunity and the enjoyable experience of filmin...</t>
         </is>
       </c>
     </row>
@@ -580,7 +595,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>NOT_SUMMARIZED</t>
+          <t>SUMMARIZED</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Dyal Singh Majithia hailed from a prominent Sikh family deeply involved in the service of Maharaja Ranjit Singh, with his relatives holding key positions within the kingdom. Leveraging his family’s influence and business acumen, he transitioned from a privileged background to become a successful real estate developer, acquiring and managing properties in Lahore. His career culminated in ownership ...</t>
         </is>
       </c>
     </row>
@@ -618,7 +638,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>NOT_SUMMARIZED</t>
+          <t>SUMMARIZED</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>The International Olympic Committee has announced that T20 cricket competitions for men and women will take place at the Pomona Fairplex in Los Angeles from July 12 to July 29, 2028, with medal matches on July 20 and 29.  This marks cricket’s second Olympic appearance after a 128-year hiatus, and will involve 6 teams per category.  Details regarding qualification for the LA28 games are still being...</t>
         </is>
       </c>
     </row>
@@ -656,7 +681,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>NOT_SUMMARIZED</t>
+          <t>SUMMARIZED</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>The Artist Event Cricket League (AECL) is launching its 7th season on September 13, 2025, featuring a celebrity team versus Team Samarthanam, the visually challenged cricket champions. The launch event included prominent figures from entertainment, sports, and government, alongside the unveiling of a commemorative book celebrating the league’s history. This season promises a significant cash prize...</t>
         </is>
       </c>
     </row>
@@ -694,7 +724,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>NOT_SUMMARIZED</t>
+          <t>SUMMARIZED</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Indian stock indices Sensex and Nifty closed slightly higher due to cautious investor sentiment amid global market weakness and tariff concerns. Tech Mahindra and Infosys were key gainers, particularly with Tech Mahindra’s strong financial results announced after market close. The day’s trading was characterized by a mixed performance, with several large companies experiencing declines.</t>
         </is>
       </c>
     </row>
@@ -732,7 +767,12 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>NOT_SUMMARIZED</t>
+          <t>SUMMARIZED</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>The FBI has identified three senior Iranian intelligence officers – Reza Amiri Moghadam, Taghi Daneshvar, and Gholamhossein Mohammadnia – as playing key roles in the 2007 abduction of Robert Levinson. These individuals, including a former ambassador to Pakistan and Albania, allegedly facilitated Levinson’s disappearance and concealed Iran’s involvement. The FBI continues to pursue accountability f...</t>
         </is>
       </c>
     </row>
@@ -770,7 +810,12 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>NOT_SUMMARIZED</t>
+          <t>SUMMARIZED</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Taiwan’s financial exposure to China decreased significantly by the end of May, dropping nearly 20% to NT$828.39 billion due to concerns about China’s economic slowdown and property market instability. This decline, particularly in interbank loans and investments in marketable securities, resulted in a record low exposure-to-net-worth ratio for Taiwanese banks and insurers. The reduction reflects ...</t>
         </is>
       </c>
     </row>
@@ -808,7 +853,12 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>NOT_SUMMARIZED</t>
+          <t>SUMMARIZED</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>The Union Cabinet approved the Prime Minister Dhan-Dhaanya Krishi Yojana, a program designed to boost agricultural productivity and sustainability across 100 identified districts.  This initiative, costing Rs 24,000 crore annually for six years, will utilize a coordinated approach involving existing schemes and private sector partnerships. The scheme aims to support 1.7 crore farmers through impro...</t>
         </is>
       </c>
     </row>
@@ -846,7 +896,12 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>NOT_SUMMARIZED</t>
+          <t>SUMMARIZED</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>“Chhoriyan Chali Gaon” is a new reality series featuring twelve urban women who will live for 60 days in a traditional Indian village, foregoing modern conveniences and embracing rural life. The show aims to explore cultural immersion, personal transformation, and social dynamics through challenging daily tasks and integration with village customs. Actor Rannvijay Singha will host, emphasizing the...</t>
         </is>
       </c>
     </row>
@@ -887,6 +942,7 @@
           <t>NOT_SUMMARIZED</t>
         </is>
       </c>
+      <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -925,6 +981,7 @@
           <t>NOT_SUMMARIZED</t>
         </is>
       </c>
+      <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -963,6 +1020,7 @@
           <t>NOT_SUMMARIZED</t>
         </is>
       </c>
+      <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1001,6 +1059,7 @@
           <t>NOT_SUMMARIZED</t>
         </is>
       </c>
+      <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1039,6 +1098,7 @@
           <t>NOT_SUMMARIZED</t>
         </is>
       </c>
+      <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1077,6 +1137,7 @@
           <t>NOT_SUMMARIZED</t>
         </is>
       </c>
+      <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1115,6 +1176,7 @@
           <t>NOT_SUMMARIZED</t>
         </is>
       </c>
+      <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1139,7 +1201,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>The security forces on Wednesday achieved a major success in their operation against Maoists as 27 Naxals, including topmost leader Nambala Keshav Rao, aka Basavaraju, were killed in an encounter in the Abujhmad region of Chhattisgarh on the border of Narayanpur and Bijapur districts. A jawan of the Chhattisgarh Police’s District Reserve Guard (DRG) was also killed while a few other personnel sustained injuries in the encounter that had begun several days ago, sources in the state police said. The killing of Keshav Rao, a CPI-Maoist general secretary, has come as a shot in the arm for the security forces as they had recently busted a long-time base of the Naxalites located in Koreguttalu Hills of Bijapur district in Chhattisgarh (bordering Telangana). Thirtyone Naxals were killed and a huge cache of arms, ammunitions and explosives recovered. Four factories where weapons were being manufactured were also unearthed under the three-week-long offensive named Operation Black Forest. Keshav Raocarried a bounty of Rs 1.5 crore and was wanted in connection with several deadly attacks on security forces across multiple states. A native of Jiyyannapet village in Andhra Pradesh's Srikakulam district, he was the son of a school teacher. He studied engineering at Warangal Regional Engineering College (REC) before being drawn into student activism in the 1980s. After being arrested during a student union protest in 1980, he went underground and joined the Naxals. Over the next four decades, Rao rose through the ranks and became known for his meticulous planning, ruthless ambushes, expertise in jungle warfare and making IEDs. Security officials believe he was the mastermind behind the 2010 Dantewada attack, one of the deadliest ever on Indian forces, in which 76 CRPF jawans were killed in Chhattisgarh. Despite the massive bounty, Rao managed to remain elusive for decades. The National Investigation Agency (NIA) had no recent photographs or confirmed details about his age. Prime M</t>
+          <t>The security forces on Wednesday achieved a major success in their operation against Maoists as 27 Naxals, including topmost leader Nambala Keshav Rao, aka Basavaraju, were killed in an encounter in the Abujhmad region of Chhattisgarh on the border of Narayanpur and Bijapur districts.AdvertisementA jawan of the Chhattisgarh Police’s District Reserve Guard (DRG) was also killed while a few other personnel sustained injuries in the encounter that had begun several days ago, sources in the state police said.The killing of Keshav Rao, a CPI-Maoist general secretary, has come as a shot in the arm for the security forces as they had recently busted a long-time base of the Naxalites located in Koreguttalu Hills of Bijapur district in Chhattisgarh (bordering Telangana). Thirtyone Naxals were killed and a huge cache of arms, ammunitions and explosives recovered. Four factories where weapons were being manufactured were also unearthed under the three-week-long offensive named Operation Black Forest.AdvertisementKeshav Raocarried a bounty of Rs 1.5 crore and was wanted in connection with several deadly attacks on security forces across multiple states. A native of Jiyyannapet village in Andhra Pradesh's Srikakulam district, he was the son of a school teacher. He studied engineering at Warangal Regional Engineering College (REC) before being drawn into student activism in the 1980s.After being arrested during a student union protest in 1980, he went underground and joined the Naxals. Over the next four decades, Rao rose through the ranks and became known for his meticulous planning, ruthless ambushes, expertise in jungle warfare and making IEDs.AdvertisementSecurity officials believe he was the mastermind behind the 2010 Dantewada attack, one of the deadliest ever on Indian forces, in which 76 CRPF jawans were killed in Chhattisgarh. Despite the massive bounty, Rao managed to remain elusive for decades. The National Investigation Agency (NIA) had no recent photographs or confirmed details about his age.Prime Minister Narendra Modi and Home Minister Amit Shah lauded the efforts of the security forces. “A landmark achievement in the battle to eliminate Naxalism. Our security forces have neutralised 27 dreaded Maoists, including Nambala Keshav Rao, alias Basavaraju, the general secretary of CPI-Maoist, topmost leader, and the backbone of the Naxal movement. This is the first time in three decades of Bharat's battle against Naxalism that a general secretary-ranked leader has been neutralised. I applaud our brave security forces for this major breakthrough," Shah said in a post on X.Shah said after the completion of Operation Black Forest, 54 Naxalites had been arrested while 84 had surrendered in Chhattisgarh, Telangana and Maharashtra.Tagging Shah's post, PM Modi said, "Proud of our forces for this remarkable success. Our government is committed to eliminating the menace of Maoism and ensuring a life of peace and progress for our people."×Unlock Exclusive Insig...</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
@@ -1153,6 +1215,7 @@
           <t>NOT_SUMMARIZED</t>
         </is>
       </c>
+      <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1191,6 +1254,7 @@
           <t>NOT_SUMMARIZED</t>
         </is>
       </c>
+      <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1229,6 +1293,7 @@
           <t>NOT_SUMMARIZED</t>
         </is>
       </c>
+      <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1267,6 +1332,7 @@
           <t>NOT_SUMMARIZED</t>
         </is>
       </c>
+      <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1305,6 +1371,7 @@
           <t>NOT_SUMMARIZED</t>
         </is>
       </c>
+      <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1343,6 +1410,7 @@
           <t>NOT_SUMMARIZED</t>
         </is>
       </c>
+      <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1381,6 +1449,7 @@
           <t>NOT_SUMMARIZED</t>
         </is>
       </c>
+      <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1419,6 +1488,7 @@
           <t>NOT_SUMMARIZED</t>
         </is>
       </c>
+      <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1457,6 +1527,7 @@
           <t>NOT_SUMMARIZED</t>
         </is>
       </c>
+      <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1495,6 +1566,7 @@
           <t>NOT_SUMMARIZED</t>
         </is>
       </c>
+      <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1533,6 +1605,7 @@
           <t>NOT_SUMMARIZED</t>
         </is>
       </c>
+      <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1571,6 +1644,7 @@
           <t>NOT_SUMMARIZED</t>
         </is>
       </c>
+      <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1609,6 +1683,7 @@
           <t>NOT_SUMMARIZED</t>
         </is>
       </c>
+      <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1647,6 +1722,7 @@
           <t>NOT_SUMMARIZED</t>
         </is>
       </c>
+      <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1685,6 +1761,7 @@
           <t>NOT_SUMMARIZED</t>
         </is>
       </c>
+      <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1723,6 +1800,7 @@
           <t>NOT_SUMMARIZED</t>
         </is>
       </c>
+      <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1761,6 +1839,7 @@
           <t>NOT_SUMMARIZED</t>
         </is>
       </c>
+      <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1799,6 +1878,7 @@
           <t>NOT_SUMMARIZED</t>
         </is>
       </c>
+      <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1837,6 +1917,7 @@
           <t>NOT_SUMMARIZED</t>
         </is>
       </c>
+      <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1875,6 +1956,7 @@
           <t>NOT_SUMMARIZED</t>
         </is>
       </c>
+      <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1913,6 +1995,7 @@
           <t>NOT_SUMMARIZED</t>
         </is>
       </c>
+      <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1951,6 +2034,7 @@
           <t>NOT_SUMMARIZED</t>
         </is>
       </c>
+      <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1989,6 +2073,7 @@
           <t>NOT_SUMMARIZED</t>
         </is>
       </c>
+      <c r="I41" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
